--- a/data/history/SCRAPING_REKAP_SE2026_AMBON_20260729_161226.xlsx
+++ b/data/history/SCRAPING_REKAP_SE2026_AMBON_20260729_161226.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZULFAA\BPS\Scrapping\monitoring-petugas\data\history\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD9325C-EE22-4A86-BED0-40E2B0769D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1380EA5-73B1-4D76-836A-0E228A6F738D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20495" uniqueCount="2675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20375" uniqueCount="2675">
   <si>
     <t>userId</t>
   </si>
@@ -8384,7 +8384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1366"/>
+  <dimension ref="A1:AC1358"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
@@ -89105,37 +89105,25 @@
     </row>
     <row r="1278" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1278" t="s">
-        <v>2224</v>
+        <v>2510</v>
       </c>
       <c r="B1278" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="C1278" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="D1278" t="s">
         <v>31</v>
       </c>
       <c r="E1278" t="s">
-        <v>2226</v>
+        <v>2512</v>
       </c>
       <c r="F1278">
-        <v>207</v>
-      </c>
-      <c r="G1278">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="H1278">
-        <v>3</v>
-      </c>
-      <c r="I1278">
-        <v>18</v>
-      </c>
-      <c r="L1278">
-        <v>117</v>
-      </c>
-      <c r="M1278">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="S1278" t="s">
         <v>33</v>
@@ -89147,51 +89135,57 @@
         <v>713</v>
       </c>
       <c r="V1278" t="s">
-        <v>839</v>
+        <v>774</v>
       </c>
       <c r="W1278" t="s">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="X1278" t="s">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="Y1278" t="s">
-        <v>840</v>
+        <v>775</v>
       </c>
       <c r="Z1278" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="AA1278" t="s">
-        <v>2227</v>
+        <v>2513</v>
       </c>
       <c r="AB1278" t="s">
-        <v>842</v>
+        <v>777</v>
       </c>
       <c r="AC1278">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1279" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1279" t="s">
-        <v>2224</v>
+        <v>2510</v>
       </c>
       <c r="B1279" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="C1279" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="D1279" t="s">
         <v>31</v>
       </c>
       <c r="E1279" t="s">
-        <v>2228</v>
+        <v>2514</v>
       </c>
       <c r="F1279">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="H1279">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="I1279">
+        <v>2</v>
+      </c>
+      <c r="L1279">
+        <v>32</v>
       </c>
       <c r="S1279" t="s">
         <v>33</v>
@@ -89200,57 +89194,54 @@
         <v>34</v>
       </c>
       <c r="U1279" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1279" t="s">
-        <v>1819</v>
+        <v>774</v>
       </c>
       <c r="W1279" t="s">
-        <v>132</v>
+        <v>678</v>
       </c>
       <c r="X1279" t="s">
-        <v>132</v>
+        <v>678</v>
       </c>
       <c r="Y1279" t="s">
-        <v>1820</v>
+        <v>775</v>
       </c>
       <c r="Z1279" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="AA1279" t="s">
-        <v>2227</v>
+        <v>2513</v>
       </c>
       <c r="AB1279" t="s">
-        <v>1822</v>
+        <v>777</v>
       </c>
       <c r="AC1279">
-        <v>151</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1280" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1280" t="s">
-        <v>2224</v>
+        <v>2510</v>
       </c>
       <c r="B1280" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="C1280" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="D1280" t="s">
         <v>31</v>
       </c>
       <c r="E1280" t="s">
-        <v>2229</v>
+        <v>2515</v>
       </c>
       <c r="F1280">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="H1280">
-        <v>126</v>
-      </c>
-      <c r="I1280">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="S1280" t="s">
         <v>33</v>
@@ -89259,60 +89250,63 @@
         <v>34</v>
       </c>
       <c r="U1280" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1280" t="s">
-        <v>1819</v>
+        <v>774</v>
       </c>
       <c r="W1280" t="s">
-        <v>123</v>
+        <v>629</v>
       </c>
       <c r="X1280" t="s">
-        <v>123</v>
+        <v>629</v>
       </c>
       <c r="Y1280" t="s">
-        <v>1820</v>
+        <v>775</v>
       </c>
       <c r="Z1280" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="AA1280" t="s">
-        <v>2227</v>
+        <v>2513</v>
       </c>
       <c r="AB1280" t="s">
-        <v>1822</v>
+        <v>777</v>
       </c>
       <c r="AC1280">
-        <v>126</v>
+        <v>89</v>
       </c>
     </row>
     <row r="1281" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1281" t="s">
-        <v>2224</v>
+        <v>2510</v>
       </c>
       <c r="B1281" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="C1281" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="D1281" t="s">
         <v>31</v>
       </c>
       <c r="E1281" t="s">
-        <v>2230</v>
+        <v>2516</v>
       </c>
       <c r="F1281">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="G1281">
-        <v>48</v>
+        <v>21</v>
+      </c>
+      <c r="H1281">
+        <v>16</v>
       </c>
       <c r="I1281">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="L1281">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="S1281" t="s">
         <v>33</v>
@@ -89324,51 +89318,60 @@
         <v>713</v>
       </c>
       <c r="V1281" t="s">
-        <v>839</v>
+        <v>774</v>
       </c>
       <c r="W1281" t="s">
-        <v>460</v>
+        <v>76</v>
       </c>
       <c r="X1281" t="s">
-        <v>460</v>
+        <v>76</v>
       </c>
       <c r="Y1281" t="s">
-        <v>840</v>
+        <v>775</v>
       </c>
       <c r="Z1281" t="s">
-        <v>2225</v>
+        <v>2511</v>
       </c>
       <c r="AA1281" t="s">
-        <v>2227</v>
+        <v>2513</v>
       </c>
       <c r="AB1281" t="s">
-        <v>842</v>
+        <v>777</v>
       </c>
       <c r="AC1281">
-        <v>88</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1282" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1282" t="s">
-        <v>2224</v>
+        <v>2517</v>
       </c>
       <c r="B1282" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="C1282" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="D1282" t="s">
         <v>31</v>
       </c>
       <c r="E1282" t="s">
-        <v>2231</v>
+        <v>2519</v>
       </c>
       <c r="F1282">
-        <v>75</v>
+        <v>195</v>
+      </c>
+      <c r="G1282">
+        <v>36</v>
       </c>
       <c r="H1282">
-        <v>75</v>
+        <v>126</v>
+      </c>
+      <c r="I1282">
+        <v>12</v>
+      </c>
+      <c r="M1282">
+        <v>21</v>
       </c>
       <c r="S1282" t="s">
         <v>33</v>
@@ -89377,60 +89380,54 @@
         <v>34</v>
       </c>
       <c r="U1282" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1282" t="s">
-        <v>1819</v>
+        <v>787</v>
       </c>
       <c r="W1282" t="s">
-        <v>183</v>
+        <v>387</v>
       </c>
       <c r="X1282" t="s">
-        <v>183</v>
+        <v>387</v>
       </c>
       <c r="Y1282" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1282" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="AA1282" t="s">
-        <v>2227</v>
+        <v>2520</v>
       </c>
       <c r="AB1282" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1282">
-        <v>75</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1283" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1283" t="s">
-        <v>2224</v>
+        <v>2517</v>
       </c>
       <c r="B1283" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="C1283" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="D1283" t="s">
         <v>31</v>
       </c>
       <c r="E1283" t="s">
-        <v>2232</v>
+        <v>2521</v>
       </c>
       <c r="F1283">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="H1283">
-        <v>20</v>
-      </c>
-      <c r="I1283">
-        <v>27</v>
-      </c>
-      <c r="L1283">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="S1283" t="s">
         <v>33</v>
@@ -89439,66 +89436,63 @@
         <v>34</v>
       </c>
       <c r="U1283" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1283" t="s">
-        <v>1819</v>
+        <v>787</v>
       </c>
       <c r="W1283" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="X1283" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="Y1283" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1283" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="AA1283" t="s">
-        <v>2227</v>
+        <v>2520</v>
       </c>
       <c r="AB1283" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1283">
-        <v>44</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1284" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1284" t="s">
-        <v>2224</v>
+        <v>2517</v>
       </c>
       <c r="B1284" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="C1284" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="D1284" t="s">
         <v>31</v>
       </c>
       <c r="E1284" t="s">
-        <v>2233</v>
+        <v>2522</v>
       </c>
       <c r="F1284">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="G1284">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H1284">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="I1284">
-        <v>20</v>
-      </c>
-      <c r="L1284">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M1284">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S1284" t="s">
         <v>33</v>
@@ -89507,57 +89501,66 @@
         <v>34</v>
       </c>
       <c r="U1284" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1284" t="s">
-        <v>1819</v>
+        <v>787</v>
       </c>
       <c r="W1284" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="X1284" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="Y1284" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1284" t="s">
-        <v>2225</v>
+        <v>2518</v>
       </c>
       <c r="AA1284" t="s">
-        <v>2227</v>
+        <v>2520</v>
       </c>
       <c r="AB1284" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1284">
-        <v>36</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1285" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1285" t="s">
-        <v>2224</v>
+        <v>2523</v>
       </c>
       <c r="B1285" t="s">
-        <v>2225</v>
+        <v>2524</v>
       </c>
       <c r="C1285" t="s">
-        <v>2225</v>
+        <v>2524</v>
       </c>
       <c r="D1285" t="s">
         <v>31</v>
       </c>
       <c r="E1285" t="s">
-        <v>2234</v>
+        <v>2525</v>
       </c>
       <c r="F1285">
-        <v>2</v>
+        <v>282</v>
+      </c>
+      <c r="G1285">
+        <v>10</v>
+      </c>
+      <c r="H1285">
+        <v>198</v>
       </c>
       <c r="I1285">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="L1285">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="M1285">
+        <v>3</v>
       </c>
       <c r="S1285" t="s">
         <v>33</v>
@@ -89566,54 +89569,54 @@
         <v>34</v>
       </c>
       <c r="U1285" t="s">
-        <v>713</v>
+        <v>35</v>
       </c>
       <c r="V1285" t="s">
-        <v>839</v>
+        <v>1541</v>
       </c>
       <c r="W1285" t="s">
-        <v>1330</v>
+        <v>2469</v>
       </c>
       <c r="X1285" t="s">
-        <v>1330</v>
+        <v>2469</v>
       </c>
       <c r="Y1285" t="s">
-        <v>840</v>
+        <v>1542</v>
       </c>
       <c r="Z1285" t="s">
-        <v>2225</v>
+        <v>2524</v>
       </c>
       <c r="AA1285" t="s">
-        <v>2227</v>
+        <v>2526</v>
       </c>
       <c r="AB1285" t="s">
-        <v>842</v>
+        <v>1544</v>
       </c>
       <c r="AC1285">
-        <v>0</v>
+        <v>244</v>
       </c>
     </row>
     <row r="1286" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1286" t="s">
-        <v>2510</v>
+        <v>2523</v>
       </c>
       <c r="B1286" t="s">
-        <v>2511</v>
+        <v>2524</v>
       </c>
       <c r="C1286" t="s">
-        <v>2511</v>
+        <v>2524</v>
       </c>
       <c r="D1286" t="s">
         <v>31</v>
       </c>
       <c r="E1286" t="s">
-        <v>2512</v>
+        <v>2527</v>
       </c>
       <c r="F1286">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="H1286">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="S1286" t="s">
         <v>33</v>
@@ -89622,60 +89625,72 @@
         <v>34</v>
       </c>
       <c r="U1286" t="s">
-        <v>713</v>
+        <v>35</v>
       </c>
       <c r="V1286" t="s">
-        <v>774</v>
+        <v>1541</v>
       </c>
       <c r="W1286" t="s">
-        <v>84</v>
+        <v>2528</v>
       </c>
       <c r="X1286" t="s">
-        <v>84</v>
+        <v>2528</v>
       </c>
       <c r="Y1286" t="s">
-        <v>775</v>
+        <v>1542</v>
       </c>
       <c r="Z1286" t="s">
-        <v>2511</v>
+        <v>2524</v>
       </c>
       <c r="AA1286" t="s">
-        <v>2513</v>
+        <v>2526</v>
       </c>
       <c r="AB1286" t="s">
-        <v>777</v>
+        <v>1544</v>
       </c>
       <c r="AC1286">
-        <v>174</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1287" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1287" t="s">
-        <v>2510</v>
+        <v>2529</v>
       </c>
       <c r="B1287" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="C1287" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="D1287" t="s">
         <v>31</v>
       </c>
       <c r="E1287" t="s">
-        <v>2514</v>
+        <v>2531</v>
       </c>
       <c r="F1287">
-        <v>119</v>
+        <v>277</v>
+      </c>
+      <c r="G1287">
+        <v>140</v>
       </c>
       <c r="H1287">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="I1287">
-        <v>2</v>
+        <v>24</v>
+      </c>
+      <c r="J1287">
+        <v>1</v>
+      </c>
+      <c r="K1287">
+        <v>1</v>
       </c>
       <c r="L1287">
-        <v>32</v>
+        <v>61</v>
+      </c>
+      <c r="M1287">
+        <v>44</v>
       </c>
       <c r="S1287" t="s">
         <v>33</v>
@@ -89684,54 +89699,66 @@
         <v>34</v>
       </c>
       <c r="U1287" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1287" t="s">
-        <v>774</v>
+        <v>249</v>
       </c>
       <c r="W1287" t="s">
-        <v>678</v>
+        <v>2532</v>
       </c>
       <c r="X1287" t="s">
-        <v>678</v>
+        <v>2532</v>
       </c>
       <c r="Y1287" t="s">
-        <v>775</v>
+        <v>251</v>
       </c>
       <c r="Z1287" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="AA1287" t="s">
-        <v>2513</v>
+        <v>2533</v>
       </c>
       <c r="AB1287" t="s">
-        <v>777</v>
+        <v>253</v>
       </c>
       <c r="AC1287">
-        <v>114</v>
+        <v>186</v>
       </c>
     </row>
     <row r="1288" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1288" t="s">
-        <v>2510</v>
+        <v>2529</v>
       </c>
       <c r="B1288" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="C1288" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="D1288" t="s">
         <v>31</v>
       </c>
       <c r="E1288" t="s">
-        <v>2515</v>
+        <v>2534</v>
       </c>
       <c r="F1288">
-        <v>89</v>
+        <v>120</v>
+      </c>
+      <c r="G1288">
+        <v>82</v>
       </c>
       <c r="H1288">
-        <v>89</v>
+        <v>2</v>
+      </c>
+      <c r="I1288">
+        <v>3</v>
+      </c>
+      <c r="L1288">
+        <v>28</v>
+      </c>
+      <c r="M1288">
+        <v>5</v>
       </c>
       <c r="S1288" t="s">
         <v>33</v>
@@ -89740,63 +89767,60 @@
         <v>34</v>
       </c>
       <c r="U1288" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1288" t="s">
-        <v>774</v>
+        <v>249</v>
       </c>
       <c r="W1288" t="s">
-        <v>629</v>
+        <v>2535</v>
       </c>
       <c r="X1288" t="s">
-        <v>629</v>
+        <v>2535</v>
       </c>
       <c r="Y1288" t="s">
-        <v>775</v>
+        <v>251</v>
       </c>
       <c r="Z1288" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="AA1288" t="s">
-        <v>2513</v>
+        <v>2533</v>
       </c>
       <c r="AB1288" t="s">
-        <v>777</v>
+        <v>253</v>
       </c>
       <c r="AC1288">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="1289" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1289" t="s">
-        <v>2510</v>
+        <v>2529</v>
       </c>
       <c r="B1289" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="C1289" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="D1289" t="s">
         <v>31</v>
       </c>
       <c r="E1289" t="s">
-        <v>2516</v>
+        <v>2536</v>
       </c>
       <c r="F1289">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="G1289">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H1289">
-        <v>16</v>
-      </c>
-      <c r="I1289">
-        <v>3</v>
-      </c>
-      <c r="L1289">
-        <v>17</v>
+        <v>98</v>
+      </c>
+      <c r="K1289">
+        <v>1</v>
       </c>
       <c r="S1289" t="s">
         <v>33</v>
@@ -89805,63 +89829,69 @@
         <v>34</v>
       </c>
       <c r="U1289" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1289" t="s">
-        <v>774</v>
+        <v>249</v>
       </c>
       <c r="W1289" t="s">
-        <v>76</v>
+        <v>2537</v>
       </c>
       <c r="X1289" t="s">
-        <v>76</v>
+        <v>2537</v>
       </c>
       <c r="Y1289" t="s">
-        <v>775</v>
+        <v>251</v>
       </c>
       <c r="Z1289" t="s">
-        <v>2511</v>
+        <v>2530</v>
       </c>
       <c r="AA1289" t="s">
-        <v>2513</v>
+        <v>2533</v>
       </c>
       <c r="AB1289" t="s">
-        <v>777</v>
+        <v>253</v>
       </c>
       <c r="AC1289">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1290" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1290" t="s">
-        <v>2517</v>
+        <v>2529</v>
       </c>
       <c r="B1290" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="C1290" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="D1290" t="s">
         <v>31</v>
       </c>
       <c r="E1290" t="s">
-        <v>2519</v>
+        <v>2538</v>
       </c>
       <c r="F1290">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="G1290">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="H1290">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="I1290">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="J1290">
+        <v>2</v>
+      </c>
+      <c r="L1290">
+        <v>20</v>
       </c>
       <c r="M1290">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S1290" t="s">
         <v>33</v>
@@ -89870,54 +89900,60 @@
         <v>34</v>
       </c>
       <c r="U1290" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1290" t="s">
-        <v>787</v>
+        <v>249</v>
       </c>
       <c r="W1290" t="s">
-        <v>387</v>
+        <v>2539</v>
       </c>
       <c r="X1290" t="s">
-        <v>387</v>
+        <v>2539</v>
       </c>
       <c r="Y1290" t="s">
-        <v>716</v>
+        <v>251</v>
       </c>
       <c r="Z1290" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="AA1290" t="s">
-        <v>2520</v>
+        <v>2533</v>
       </c>
       <c r="AB1290" t="s">
-        <v>718</v>
+        <v>253</v>
       </c>
       <c r="AC1290">
-        <v>187</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1291" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1291" t="s">
-        <v>2517</v>
+        <v>2529</v>
       </c>
       <c r="B1291" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="C1291" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="D1291" t="s">
         <v>31</v>
       </c>
       <c r="E1291" t="s">
-        <v>2521</v>
+        <v>2540</v>
       </c>
       <c r="F1291">
-        <v>121</v>
-      </c>
-      <c r="H1291">
-        <v>121</v>
+        <v>98</v>
+      </c>
+      <c r="G1291">
+        <v>6</v>
+      </c>
+      <c r="I1291">
+        <v>26</v>
+      </c>
+      <c r="L1291">
+        <v>66</v>
       </c>
       <c r="S1291" t="s">
         <v>33</v>
@@ -89926,63 +89962,54 @@
         <v>34</v>
       </c>
       <c r="U1291" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1291" t="s">
-        <v>787</v>
+        <v>249</v>
       </c>
       <c r="W1291" t="s">
-        <v>117</v>
+        <v>2541</v>
       </c>
       <c r="X1291" t="s">
-        <v>117</v>
+        <v>2541</v>
       </c>
       <c r="Y1291" t="s">
-        <v>716</v>
+        <v>251</v>
       </c>
       <c r="Z1291" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="AA1291" t="s">
-        <v>2520</v>
+        <v>2533</v>
       </c>
       <c r="AB1291" t="s">
-        <v>718</v>
+        <v>253</v>
       </c>
       <c r="AC1291">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="1292" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1292" t="s">
-        <v>2517</v>
+        <v>2529</v>
       </c>
       <c r="B1292" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="C1292" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="D1292" t="s">
         <v>31</v>
       </c>
       <c r="E1292" t="s">
-        <v>2522</v>
+        <v>2542</v>
       </c>
       <c r="F1292">
-        <v>83</v>
-      </c>
-      <c r="G1292">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="H1292">
-        <v>70</v>
-      </c>
-      <c r="I1292">
-        <v>5</v>
-      </c>
-      <c r="M1292">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="S1292" t="s">
         <v>33</v>
@@ -89991,66 +90018,63 @@
         <v>34</v>
       </c>
       <c r="U1292" t="s">
-        <v>713</v>
+        <v>110</v>
       </c>
       <c r="V1292" t="s">
-        <v>787</v>
+        <v>249</v>
       </c>
       <c r="W1292" t="s">
-        <v>185</v>
+        <v>2543</v>
       </c>
       <c r="X1292" t="s">
-        <v>185</v>
+        <v>2543</v>
       </c>
       <c r="Y1292" t="s">
-        <v>716</v>
+        <v>251</v>
       </c>
       <c r="Z1292" t="s">
-        <v>2518</v>
+        <v>2530</v>
       </c>
       <c r="AA1292" t="s">
-        <v>2520</v>
+        <v>2533</v>
       </c>
       <c r="AB1292" t="s">
-        <v>718</v>
+        <v>253</v>
       </c>
       <c r="AC1292">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1293" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1293" t="s">
-        <v>2523</v>
+        <v>2529</v>
       </c>
       <c r="B1293" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="C1293" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="D1293" t="s">
         <v>31</v>
       </c>
       <c r="E1293" t="s">
-        <v>2525</v>
+        <v>2544</v>
       </c>
       <c r="F1293">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="G1293">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H1293">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="I1293">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="L1293">
-        <v>39</v>
-      </c>
-      <c r="M1293">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S1293" t="s">
         <v>33</v>
@@ -90059,87 +90083,93 @@
         <v>34</v>
       </c>
       <c r="U1293" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="V1293" t="s">
-        <v>1541</v>
+        <v>249</v>
       </c>
       <c r="W1293" t="s">
-        <v>2469</v>
+        <v>2545</v>
       </c>
       <c r="X1293" t="s">
-        <v>2469</v>
+        <v>2545</v>
       </c>
       <c r="Y1293" t="s">
-        <v>1542</v>
+        <v>251</v>
       </c>
       <c r="Z1293" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="AA1293" t="s">
-        <v>2526</v>
+        <v>2533</v>
       </c>
       <c r="AB1293" t="s">
-        <v>1544</v>
+        <v>253</v>
       </c>
       <c r="AC1293">
-        <v>244</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1294" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1294" t="s">
-        <v>2523</v>
+        <v>2529</v>
       </c>
       <c r="B1294" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="C1294" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="D1294" t="s">
         <v>31</v>
       </c>
       <c r="E1294" t="s">
-        <v>2527</v>
+        <v>2546</v>
       </c>
       <c r="F1294">
+        <v>74</v>
+      </c>
+      <c r="G1294">
+        <v>5</v>
+      </c>
+      <c r="H1294">
+        <v>65</v>
+      </c>
+      <c r="I1294">
+        <v>4</v>
+      </c>
+      <c r="S1294" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1294" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1294" t="s">
         <v>110</v>
       </c>
-      <c r="H1294">
-        <v>110</v>
-      </c>
-      <c r="S1294" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1294" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1294" t="s">
-        <v>35</v>
-      </c>
       <c r="V1294" t="s">
-        <v>1541</v>
+        <v>249</v>
       </c>
       <c r="W1294" t="s">
-        <v>2528</v>
+        <v>2547</v>
       </c>
       <c r="X1294" t="s">
-        <v>2528</v>
+        <v>2547</v>
       </c>
       <c r="Y1294" t="s">
-        <v>1542</v>
+        <v>251</v>
       </c>
       <c r="Z1294" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="AA1294" t="s">
-        <v>2526</v>
+        <v>2533</v>
       </c>
       <c r="AB1294" t="s">
-        <v>1544</v>
+        <v>253</v>
       </c>
       <c r="AC1294">
-        <v>110</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1295" spans="1:29" x14ac:dyDescent="0.3">
@@ -90156,31 +90186,16 @@
         <v>31</v>
       </c>
       <c r="E1295" t="s">
-        <v>2531</v>
+        <v>2548</v>
       </c>
       <c r="F1295">
-        <v>277</v>
+        <v>9</v>
       </c>
       <c r="G1295">
-        <v>140</v>
-      </c>
-      <c r="H1295">
         <v>6</v>
       </c>
-      <c r="I1295">
-        <v>24</v>
-      </c>
-      <c r="J1295">
-        <v>1</v>
-      </c>
-      <c r="K1295">
-        <v>1</v>
-      </c>
-      <c r="L1295">
-        <v>61</v>
-      </c>
       <c r="M1295">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="S1295" t="s">
         <v>33</v>
@@ -90195,10 +90210,10 @@
         <v>249</v>
       </c>
       <c r="W1295" t="s">
-        <v>2532</v>
+        <v>2549</v>
       </c>
       <c r="X1295" t="s">
-        <v>2532</v>
+        <v>2549</v>
       </c>
       <c r="Y1295" t="s">
         <v>251</v>
@@ -90213,42 +90228,42 @@
         <v>253</v>
       </c>
       <c r="AC1295">
-        <v>186</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1296" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1296" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1296" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1296" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1296" t="s">
         <v>31</v>
       </c>
       <c r="E1296" t="s">
-        <v>2534</v>
+        <v>2552</v>
       </c>
       <c r="F1296">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G1296">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H1296">
         <v>2</v>
       </c>
       <c r="I1296">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L1296">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="M1296">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S1296" t="s">
         <v>33</v>
@@ -90263,54 +90278,60 @@
         <v>249</v>
       </c>
       <c r="W1296" t="s">
-        <v>2535</v>
+        <v>2553</v>
       </c>
       <c r="X1296" t="s">
-        <v>2535</v>
+        <v>2553</v>
       </c>
       <c r="Y1296" t="s">
         <v>251</v>
       </c>
       <c r="Z1296" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1296" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1296" t="s">
         <v>253</v>
       </c>
       <c r="AC1296">
-        <v>100</v>
+        <v>147</v>
       </c>
     </row>
     <row r="1297" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1297" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1297" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1297" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1297" t="s">
         <v>31</v>
       </c>
       <c r="E1297" t="s">
-        <v>2536</v>
+        <v>2555</v>
       </c>
       <c r="F1297">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="G1297">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="H1297">
-        <v>98</v>
-      </c>
-      <c r="K1297">
         <v>1</v>
+      </c>
+      <c r="I1297">
+        <v>8</v>
+      </c>
+      <c r="L1297">
+        <v>32</v>
+      </c>
+      <c r="M1297">
+        <v>6</v>
       </c>
       <c r="S1297" t="s">
         <v>33</v>
@@ -90325,63 +90346,57 @@
         <v>249</v>
       </c>
       <c r="W1297" t="s">
-        <v>2537</v>
+        <v>2556</v>
       </c>
       <c r="X1297" t="s">
-        <v>2537</v>
+        <v>2556</v>
       </c>
       <c r="Y1297" t="s">
         <v>251</v>
       </c>
       <c r="Z1297" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1297" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1297" t="s">
         <v>253</v>
       </c>
       <c r="AC1297">
-        <v>114</v>
+        <v>139</v>
       </c>
     </row>
     <row r="1298" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1298" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1298" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1298" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1298" t="s">
         <v>31</v>
       </c>
       <c r="E1298" t="s">
-        <v>2538</v>
+        <v>2557</v>
       </c>
       <c r="F1298">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="G1298">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H1298">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="I1298">
-        <v>10</v>
-      </c>
-      <c r="J1298">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="L1298">
-        <v>20</v>
-      </c>
-      <c r="M1298">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="S1298" t="s">
         <v>33</v>
@@ -90396,54 +90411,54 @@
         <v>249</v>
       </c>
       <c r="W1298" t="s">
-        <v>2539</v>
+        <v>2558</v>
       </c>
       <c r="X1298" t="s">
-        <v>2539</v>
+        <v>2558</v>
       </c>
       <c r="Y1298" t="s">
         <v>251</v>
       </c>
       <c r="Z1298" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1298" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1298" t="s">
         <v>253</v>
       </c>
       <c r="AC1298">
-        <v>75</v>
+        <v>136</v>
       </c>
     </row>
     <row r="1299" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1299" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1299" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1299" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1299" t="s">
         <v>31</v>
       </c>
       <c r="E1299" t="s">
-        <v>2540</v>
+        <v>2559</v>
       </c>
       <c r="F1299">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G1299">
+        <v>10</v>
+      </c>
+      <c r="H1299">
+        <v>96</v>
+      </c>
+      <c r="L1299">
         <v>6</v>
-      </c>
-      <c r="I1299">
-        <v>26</v>
-      </c>
-      <c r="L1299">
-        <v>66</v>
       </c>
       <c r="S1299" t="s">
         <v>33</v>
@@ -90455,51 +90470,60 @@
         <v>110</v>
       </c>
       <c r="V1299" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1299" t="s">
-        <v>2541</v>
+        <v>995</v>
       </c>
       <c r="X1299" t="s">
-        <v>2541</v>
+        <v>995</v>
       </c>
       <c r="Y1299" t="s">
         <v>251</v>
       </c>
       <c r="Z1299" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1299" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1299" t="s">
         <v>253</v>
       </c>
       <c r="AC1299">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1300" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1300" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1300" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1300" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1300" t="s">
         <v>31</v>
       </c>
       <c r="E1300" t="s">
-        <v>2542</v>
+        <v>2560</v>
       </c>
       <c r="F1300">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="G1300">
+        <v>43</v>
       </c>
       <c r="H1300">
-        <v>92</v>
+        <v>7</v>
+      </c>
+      <c r="I1300">
+        <v>12</v>
+      </c>
+      <c r="L1300">
+        <v>29</v>
       </c>
       <c r="S1300" t="s">
         <v>33</v>
@@ -90514,57 +90538,51 @@
         <v>249</v>
       </c>
       <c r="W1300" t="s">
-        <v>2543</v>
+        <v>2561</v>
       </c>
       <c r="X1300" t="s">
-        <v>2543</v>
+        <v>2561</v>
       </c>
       <c r="Y1300" t="s">
         <v>251</v>
       </c>
       <c r="Z1300" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1300" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1300" t="s">
         <v>253</v>
       </c>
       <c r="AC1300">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="1301" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1301" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1301" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1301" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1301" t="s">
         <v>31</v>
       </c>
       <c r="E1301" t="s">
-        <v>2544</v>
+        <v>2562</v>
       </c>
       <c r="F1301">
-        <v>77</v>
-      </c>
-      <c r="G1301">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="H1301">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="I1301">
-        <v>25</v>
-      </c>
-      <c r="L1301">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S1301" t="s">
         <v>33</v>
@@ -90579,54 +90597,57 @@
         <v>249</v>
       </c>
       <c r="W1301" t="s">
-        <v>2545</v>
+        <v>2563</v>
       </c>
       <c r="X1301" t="s">
-        <v>2545</v>
+        <v>2563</v>
       </c>
       <c r="Y1301" t="s">
         <v>251</v>
       </c>
       <c r="Z1301" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1301" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1301" t="s">
         <v>253</v>
       </c>
       <c r="AC1301">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1302" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1302" t="s">
-        <v>2529</v>
+        <v>2550</v>
       </c>
       <c r="B1302" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="C1302" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="D1302" t="s">
         <v>31</v>
       </c>
       <c r="E1302" t="s">
-        <v>2546</v>
+        <v>2564</v>
       </c>
       <c r="F1302">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G1302">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H1302">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="I1302">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="L1302">
+        <v>23</v>
       </c>
       <c r="S1302" t="s">
         <v>33</v>
@@ -90641,51 +90662,60 @@
         <v>249</v>
       </c>
       <c r="W1302" t="s">
-        <v>2547</v>
+        <v>2565</v>
       </c>
       <c r="X1302" t="s">
-        <v>2547</v>
+        <v>2565</v>
       </c>
       <c r="Y1302" t="s">
         <v>251</v>
       </c>
       <c r="Z1302" t="s">
-        <v>2530</v>
+        <v>2551</v>
       </c>
       <c r="AA1302" t="s">
-        <v>2533</v>
+        <v>2554</v>
       </c>
       <c r="AB1302" t="s">
         <v>253</v>
       </c>
       <c r="AC1302">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="1303" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1303" t="s">
-        <v>2529</v>
+        <v>2566</v>
       </c>
       <c r="B1303" t="s">
-        <v>2530</v>
+        <v>2567</v>
       </c>
       <c r="C1303" t="s">
-        <v>2530</v>
+        <v>2567</v>
       </c>
       <c r="D1303" t="s">
         <v>31</v>
       </c>
       <c r="E1303" t="s">
-        <v>2548</v>
+        <v>2568</v>
       </c>
       <c r="F1303">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="G1303">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="H1303">
+        <v>26</v>
+      </c>
+      <c r="I1303">
+        <v>7</v>
+      </c>
+      <c r="L1303">
+        <v>130</v>
       </c>
       <c r="M1303">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S1303" t="s">
         <v>33</v>
@@ -90697,63 +90727,57 @@
         <v>110</v>
       </c>
       <c r="V1303" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="W1303" t="s">
-        <v>2549</v>
+        <v>281</v>
       </c>
       <c r="X1303" t="s">
-        <v>2549</v>
+        <v>281</v>
       </c>
       <c r="Y1303" t="s">
         <v>251</v>
       </c>
       <c r="Z1303" t="s">
-        <v>2530</v>
+        <v>2567</v>
       </c>
       <c r="AA1303" t="s">
-        <v>2533</v>
+        <v>2569</v>
       </c>
       <c r="AB1303" t="s">
         <v>253</v>
       </c>
       <c r="AC1303">
-        <v>4</v>
+        <v>156</v>
       </c>
     </row>
     <row r="1304" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1304" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1304" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1304" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1304" t="s">
         <v>31</v>
       </c>
       <c r="E1304" t="s">
-        <v>2552</v>
+        <v>2570</v>
       </c>
       <c r="F1304">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G1304">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="H1304">
-        <v>2</v>
-      </c>
-      <c r="I1304">
-        <v>11</v>
-      </c>
-      <c r="L1304">
-        <v>83</v>
-      </c>
-      <c r="M1304">
-        <v>9</v>
+        <v>139</v>
+      </c>
+      <c r="K1304">
+        <v>1</v>
       </c>
       <c r="S1304" t="s">
         <v>33</v>
@@ -90765,63 +90789,54 @@
         <v>110</v>
       </c>
       <c r="V1304" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1304" t="s">
-        <v>2553</v>
+        <v>357</v>
       </c>
       <c r="X1304" t="s">
-        <v>2553</v>
+        <v>357</v>
       </c>
       <c r="Y1304" t="s">
         <v>251</v>
       </c>
       <c r="Z1304" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1304" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1304" t="s">
         <v>253</v>
       </c>
       <c r="AC1304">
-        <v>147</v>
+        <v>167</v>
       </c>
     </row>
     <row r="1305" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1305" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1305" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1305" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1305" t="s">
         <v>31</v>
       </c>
       <c r="E1305" t="s">
-        <v>2555</v>
+        <v>2571</v>
       </c>
       <c r="F1305">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="G1305">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="H1305">
-        <v>1</v>
-      </c>
-      <c r="I1305">
-        <v>8</v>
-      </c>
-      <c r="L1305">
-        <v>32</v>
-      </c>
-      <c r="M1305">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="S1305" t="s">
         <v>33</v>
@@ -90833,60 +90848,63 @@
         <v>110</v>
       </c>
       <c r="V1305" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1305" t="s">
-        <v>2556</v>
+        <v>348</v>
       </c>
       <c r="X1305" t="s">
-        <v>2556</v>
+        <v>348</v>
       </c>
       <c r="Y1305" t="s">
         <v>251</v>
       </c>
       <c r="Z1305" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1305" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1305" t="s">
         <v>253</v>
       </c>
       <c r="AC1305">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1306" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1306" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1306" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1306" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1306" t="s">
         <v>31</v>
       </c>
       <c r="E1306" t="s">
-        <v>2557</v>
+        <v>2572</v>
       </c>
       <c r="F1306">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="G1306">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H1306">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="I1306">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L1306">
-        <v>44</v>
+        <v>37</v>
+      </c>
+      <c r="M1306">
+        <v>11</v>
       </c>
       <c r="S1306" t="s">
         <v>33</v>
@@ -90898,57 +90916,57 @@
         <v>110</v>
       </c>
       <c r="V1306" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="W1306" t="s">
-        <v>2558</v>
+        <v>191</v>
       </c>
       <c r="X1306" t="s">
-        <v>2558</v>
+        <v>191</v>
       </c>
       <c r="Y1306" t="s">
         <v>251</v>
       </c>
       <c r="Z1306" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1306" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1306" t="s">
         <v>253</v>
       </c>
       <c r="AC1306">
-        <v>136</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1307" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1307" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1307" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1307" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1307" t="s">
         <v>31</v>
       </c>
       <c r="E1307" t="s">
-        <v>2559</v>
+        <v>2573</v>
       </c>
       <c r="F1307">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G1307">
-        <v>10</v>
-      </c>
-      <c r="H1307">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="L1307">
-        <v>6</v>
+        <v>52</v>
+      </c>
+      <c r="M1307">
+        <v>11</v>
       </c>
       <c r="S1307" t="s">
         <v>33</v>
@@ -90960,7 +90978,7 @@
         <v>110</v>
       </c>
       <c r="V1307" t="s">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="W1307" t="s">
         <v>995</v>
@@ -90972,48 +90990,45 @@
         <v>251</v>
       </c>
       <c r="Z1307" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1307" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1307" t="s">
         <v>253</v>
       </c>
       <c r="AC1307">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1308" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1308" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1308" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1308" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1308" t="s">
         <v>31</v>
       </c>
       <c r="E1308" t="s">
-        <v>2560</v>
+        <v>2574</v>
       </c>
       <c r="F1308">
-        <v>91</v>
-      </c>
-      <c r="G1308">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H1308">
+        <v>53</v>
+      </c>
+      <c r="I1308">
+        <v>38</v>
+      </c>
+      <c r="L1308">
         <v>7</v>
-      </c>
-      <c r="I1308">
-        <v>12</v>
-      </c>
-      <c r="L1308">
-        <v>29</v>
       </c>
       <c r="S1308" t="s">
         <v>33</v>
@@ -91025,54 +91040,63 @@
         <v>110</v>
       </c>
       <c r="V1308" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1308" t="s">
-        <v>2561</v>
+        <v>355</v>
       </c>
       <c r="X1308" t="s">
-        <v>2561</v>
+        <v>355</v>
       </c>
       <c r="Y1308" t="s">
         <v>251</v>
       </c>
       <c r="Z1308" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1308" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1308" t="s">
         <v>253</v>
       </c>
       <c r="AC1308">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1309" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1309" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1309" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1309" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1309" t="s">
         <v>31</v>
       </c>
       <c r="E1309" t="s">
-        <v>2562</v>
+        <v>2575</v>
       </c>
       <c r="F1309">
-        <v>63</v>
+        <v>67</v>
+      </c>
+      <c r="G1309">
+        <v>9</v>
       </c>
       <c r="H1309">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="I1309">
-        <v>3</v>
+        <v>13</v>
+      </c>
+      <c r="L1309">
+        <v>34</v>
+      </c>
+      <c r="M1309">
+        <v>7</v>
       </c>
       <c r="S1309" t="s">
         <v>33</v>
@@ -91084,60 +91108,51 @@
         <v>110</v>
       </c>
       <c r="V1309" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1309" t="s">
-        <v>2563</v>
+        <v>353</v>
       </c>
       <c r="X1309" t="s">
-        <v>2563</v>
+        <v>353</v>
       </c>
       <c r="Y1309" t="s">
         <v>251</v>
       </c>
       <c r="Z1309" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1309" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1309" t="s">
         <v>253</v>
       </c>
       <c r="AC1309">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1310" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1310" t="s">
-        <v>2550</v>
+        <v>2566</v>
       </c>
       <c r="B1310" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="C1310" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="D1310" t="s">
         <v>31</v>
       </c>
       <c r="E1310" t="s">
-        <v>2564</v>
+        <v>2576</v>
       </c>
       <c r="F1310">
-        <v>62</v>
-      </c>
-      <c r="G1310">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="H1310">
-        <v>4</v>
-      </c>
-      <c r="I1310">
-        <v>9</v>
-      </c>
-      <c r="L1310">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="S1310" t="s">
         <v>33</v>
@@ -91149,28 +91164,28 @@
         <v>110</v>
       </c>
       <c r="V1310" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="W1310" t="s">
-        <v>2565</v>
+        <v>191</v>
       </c>
       <c r="X1310" t="s">
-        <v>2565</v>
+        <v>191</v>
       </c>
       <c r="Y1310" t="s">
         <v>251</v>
       </c>
       <c r="Z1310" t="s">
-        <v>2551</v>
+        <v>2567</v>
       </c>
       <c r="AA1310" t="s">
-        <v>2554</v>
+        <v>2569</v>
       </c>
       <c r="AB1310" t="s">
         <v>253</v>
       </c>
       <c r="AC1310">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1311" spans="1:29" x14ac:dyDescent="0.3">
@@ -91187,25 +91202,13 @@
         <v>31</v>
       </c>
       <c r="E1311" t="s">
-        <v>2568</v>
+        <v>2577</v>
       </c>
       <c r="F1311">
-        <v>182</v>
-      </c>
-      <c r="G1311">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H1311">
-        <v>26</v>
-      </c>
-      <c r="I1311">
-        <v>7</v>
-      </c>
-      <c r="L1311">
-        <v>130</v>
-      </c>
-      <c r="M1311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S1311" t="s">
         <v>33</v>
@@ -91217,13 +91220,13 @@
         <v>110</v>
       </c>
       <c r="V1311" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="W1311" t="s">
-        <v>281</v>
+        <v>1330</v>
       </c>
       <c r="X1311" t="s">
-        <v>281</v>
+        <v>1330</v>
       </c>
       <c r="Y1311" t="s">
         <v>251</v>
@@ -91238,36 +91241,42 @@
         <v>253</v>
       </c>
       <c r="AC1311">
-        <v>156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1312" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1312" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1312" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1312" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1312" t="s">
         <v>31</v>
       </c>
       <c r="E1312" t="s">
-        <v>2570</v>
+        <v>2580</v>
       </c>
       <c r="F1312">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="G1312">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H1312">
-        <v>139</v>
-      </c>
-      <c r="K1312">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="I1312">
+        <v>11</v>
+      </c>
+      <c r="L1312">
+        <v>121</v>
+      </c>
+      <c r="M1312">
+        <v>16</v>
       </c>
       <c r="S1312" t="s">
         <v>33</v>
@@ -91282,51 +91291,57 @@
         <v>273</v>
       </c>
       <c r="W1312" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="X1312" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="Y1312" t="s">
         <v>251</v>
       </c>
       <c r="Z1312" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1312" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1312" t="s">
         <v>253</v>
       </c>
       <c r="AC1312">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="1313" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1313" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1313" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1313" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1313" t="s">
         <v>31</v>
       </c>
       <c r="E1313" t="s">
-        <v>2571</v>
+        <v>2582</v>
       </c>
       <c r="F1313">
-        <v>118</v>
+        <v>166</v>
       </c>
       <c r="G1313">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="H1313">
-        <v>57</v>
+        <v>83</v>
+      </c>
+      <c r="I1313">
+        <v>44</v>
+      </c>
+      <c r="L1313">
+        <v>19</v>
       </c>
       <c r="S1313" t="s">
         <v>33</v>
@@ -91341,60 +91356,69 @@
         <v>273</v>
       </c>
       <c r="W1313" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="X1313" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="Y1313" t="s">
         <v>251</v>
       </c>
       <c r="Z1313" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1313" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1313" t="s">
         <v>253</v>
       </c>
       <c r="AC1313">
-        <v>118</v>
+        <v>162</v>
       </c>
     </row>
     <row r="1314" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1314" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1314" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1314" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1314" t="s">
         <v>31</v>
       </c>
       <c r="E1314" t="s">
-        <v>2572</v>
+        <v>2583</v>
       </c>
       <c r="F1314">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="G1314">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="H1314">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I1314">
         <v>3</v>
       </c>
+      <c r="J1314">
+        <v>1</v>
+      </c>
+      <c r="K1314">
+        <v>1</v>
+      </c>
       <c r="L1314">
-        <v>37</v>
+        <v>115</v>
       </c>
       <c r="M1314">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="N1314">
+        <v>4</v>
       </c>
       <c r="S1314" t="s">
         <v>33</v>
@@ -91406,54 +91430,63 @@
         <v>110</v>
       </c>
       <c r="V1314" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="W1314" t="s">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="X1314" t="s">
-        <v>191</v>
+        <v>340</v>
       </c>
       <c r="Y1314" t="s">
         <v>251</v>
       </c>
       <c r="Z1314" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1314" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1314" t="s">
         <v>253</v>
       </c>
       <c r="AC1314">
-        <v>78</v>
+        <v>144</v>
       </c>
     </row>
     <row r="1315" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1315" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1315" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1315" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1315" t="s">
         <v>31</v>
       </c>
       <c r="E1315" t="s">
-        <v>2573</v>
+        <v>2584</v>
       </c>
       <c r="F1315">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="G1315">
-        <v>40</v>
+        <v>63</v>
+      </c>
+      <c r="H1315">
+        <v>24</v>
+      </c>
+      <c r="I1315">
+        <v>6</v>
+      </c>
+      <c r="K1315">
+        <v>1</v>
       </c>
       <c r="L1315">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="M1315">
         <v>11</v>
@@ -91468,57 +91501,51 @@
         <v>110</v>
       </c>
       <c r="V1315" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="W1315" t="s">
-        <v>995</v>
+        <v>336</v>
       </c>
       <c r="X1315" t="s">
-        <v>995</v>
+        <v>336</v>
       </c>
       <c r="Y1315" t="s">
         <v>251</v>
       </c>
       <c r="Z1315" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1315" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1315" t="s">
         <v>253</v>
       </c>
       <c r="AC1315">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1316" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1316" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1316" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1316" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1316" t="s">
         <v>31</v>
       </c>
       <c r="E1316" t="s">
-        <v>2574</v>
+        <v>2585</v>
       </c>
       <c r="F1316">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="H1316">
-        <v>53</v>
-      </c>
-      <c r="I1316">
-        <v>38</v>
-      </c>
-      <c r="L1316">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="S1316" t="s">
         <v>33</v>
@@ -91533,60 +91560,57 @@
         <v>273</v>
       </c>
       <c r="W1316" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="X1316" t="s">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="Y1316" t="s">
         <v>251</v>
       </c>
       <c r="Z1316" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1316" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1316" t="s">
         <v>253</v>
       </c>
       <c r="AC1316">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1317" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1317" t="s">
-        <v>2566</v>
+        <v>2578</v>
       </c>
       <c r="B1317" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="C1317" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="D1317" t="s">
         <v>31</v>
       </c>
       <c r="E1317" t="s">
-        <v>2575</v>
+        <v>2586</v>
       </c>
       <c r="F1317">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G1317">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H1317">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I1317">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L1317">
-        <v>34</v>
-      </c>
-      <c r="M1317">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="S1317" t="s">
         <v>33</v>
@@ -91601,48 +91625,57 @@
         <v>273</v>
       </c>
       <c r="W1317" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="X1317" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="Y1317" t="s">
         <v>251</v>
       </c>
       <c r="Z1317" t="s">
-        <v>2567</v>
+        <v>2579</v>
       </c>
       <c r="AA1317" t="s">
-        <v>2569</v>
+        <v>2581</v>
       </c>
       <c r="AB1317" t="s">
         <v>253</v>
       </c>
       <c r="AC1317">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="1318" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1318" t="s">
-        <v>2566</v>
+        <v>2587</v>
       </c>
       <c r="B1318" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="C1318" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="D1318" t="s">
         <v>31</v>
       </c>
       <c r="E1318" t="s">
-        <v>2576</v>
+        <v>2589</v>
       </c>
       <c r="F1318">
-        <v>63</v>
+        <v>157</v>
+      </c>
+      <c r="G1318">
+        <v>93</v>
       </c>
       <c r="H1318">
-        <v>63</v>
+        <v>7</v>
+      </c>
+      <c r="I1318">
+        <v>39</v>
+      </c>
+      <c r="M1318">
+        <v>18</v>
       </c>
       <c r="S1318" t="s">
         <v>33</v>
@@ -91651,54 +91684,63 @@
         <v>34</v>
       </c>
       <c r="U1318" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1318" t="s">
-        <v>273</v>
+        <v>1819</v>
       </c>
       <c r="W1318" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="X1318" t="s">
-        <v>191</v>
+        <v>125</v>
       </c>
       <c r="Y1318" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1318" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="AA1318" t="s">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="AB1318" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1318">
-        <v>63</v>
+        <v>152</v>
       </c>
     </row>
     <row r="1319" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1319" t="s">
-        <v>2566</v>
+        <v>2587</v>
       </c>
       <c r="B1319" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="C1319" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="D1319" t="s">
         <v>31</v>
       </c>
       <c r="E1319" t="s">
-        <v>2577</v>
+        <v>2591</v>
       </c>
       <c r="F1319">
-        <v>1</v>
+        <v>122</v>
+      </c>
+      <c r="G1319">
+        <v>39</v>
       </c>
       <c r="H1319">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="I1319">
+        <v>6</v>
+      </c>
+      <c r="M1319">
+        <v>75</v>
       </c>
       <c r="S1319" t="s">
         <v>33</v>
@@ -91707,66 +91749,60 @@
         <v>34</v>
       </c>
       <c r="U1319" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1319" t="s">
-        <v>273</v>
+        <v>1853</v>
       </c>
       <c r="W1319" t="s">
-        <v>1330</v>
+        <v>2592</v>
       </c>
       <c r="X1319" t="s">
-        <v>1330</v>
+        <v>2592</v>
       </c>
       <c r="Y1319" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1319" t="s">
-        <v>2567</v>
+        <v>2588</v>
       </c>
       <c r="AA1319" t="s">
-        <v>2569</v>
+        <v>2590</v>
       </c>
       <c r="AB1319" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1319">
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1320" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1320" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1320" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1320" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1320" t="s">
         <v>31</v>
       </c>
       <c r="E1320" t="s">
-        <v>2580</v>
+        <v>2593</v>
       </c>
       <c r="F1320">
-        <v>205</v>
+        <v>107</v>
       </c>
       <c r="G1320">
-        <v>34</v>
-      </c>
-      <c r="H1320">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I1320">
-        <v>11</v>
-      </c>
-      <c r="L1320">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="M1320">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="S1320" t="s">
         <v>33</v>
@@ -91775,63 +91811,54 @@
         <v>34</v>
       </c>
       <c r="U1320" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1320" t="s">
-        <v>273</v>
+        <v>1853</v>
       </c>
       <c r="W1320" t="s">
-        <v>328</v>
+        <v>2594</v>
       </c>
       <c r="X1320" t="s">
-        <v>328</v>
+        <v>2594</v>
       </c>
       <c r="Y1320" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1320" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1320" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1320" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1320">
-        <v>187</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1321" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1321" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1321" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1321" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1321" t="s">
         <v>31</v>
       </c>
       <c r="E1321" t="s">
-        <v>2582</v>
+        <v>2595</v>
       </c>
       <c r="F1321">
-        <v>166</v>
-      </c>
-      <c r="G1321">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="H1321">
-        <v>83</v>
-      </c>
-      <c r="I1321">
-        <v>44</v>
-      </c>
-      <c r="L1321">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="S1321" t="s">
         <v>33</v>
@@ -91840,74 +91867,59 @@
         <v>34</v>
       </c>
       <c r="U1321" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1321" t="s">
-        <v>273</v>
+        <v>1853</v>
       </c>
       <c r="W1321" t="s">
-        <v>342</v>
+        <v>2596</v>
       </c>
       <c r="X1321" t="s">
-        <v>342</v>
+        <v>2596</v>
       </c>
       <c r="Y1321" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1321" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1321" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1321" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1321">
-        <v>162</v>
+        <v>68</v>
       </c>
     </row>
     <row r="1322" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1322" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1322" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1322" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1322" t="s">
         <v>31</v>
       </c>
       <c r="E1322" t="s">
-        <v>2583</v>
+        <v>2597</v>
       </c>
       <c r="F1322">
-        <v>161</v>
+        <v>63</v>
       </c>
       <c r="G1322">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="H1322">
-        <v>3</v>
-      </c>
-      <c r="I1322">
-        <v>3</v>
-      </c>
-      <c r="J1322">
-        <v>1</v>
-      </c>
-      <c r="K1322">
-        <v>1</v>
-      </c>
-      <c r="L1322">
-        <v>115</v>
+        <v>8</v>
       </c>
       <c r="M1322">
-        <v>1</v>
-      </c>
-      <c r="N1322">
         <v>4</v>
       </c>
       <c r="S1322" t="s">
@@ -91917,69 +91929,54 @@
         <v>34</v>
       </c>
       <c r="U1322" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1322" t="s">
-        <v>273</v>
+        <v>1887</v>
       </c>
       <c r="W1322" t="s">
-        <v>340</v>
+        <v>995</v>
       </c>
       <c r="X1322" t="s">
-        <v>340</v>
+        <v>995</v>
       </c>
       <c r="Y1322" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1322" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1322" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1322" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1322">
-        <v>144</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1323" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1323" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1323" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1323" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1323" t="s">
         <v>31</v>
       </c>
       <c r="E1323" t="s">
-        <v>2584</v>
+        <v>2598</v>
       </c>
       <c r="F1323">
-        <v>128</v>
-      </c>
-      <c r="G1323">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H1323">
-        <v>24</v>
-      </c>
-      <c r="I1323">
-        <v>6</v>
-      </c>
-      <c r="K1323">
-        <v>1</v>
-      </c>
-      <c r="L1323">
-        <v>23</v>
-      </c>
-      <c r="M1323">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="S1323" t="s">
         <v>33</v>
@@ -91988,54 +91985,66 @@
         <v>34</v>
       </c>
       <c r="U1323" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1323" t="s">
-        <v>273</v>
+        <v>1853</v>
       </c>
       <c r="W1323" t="s">
-        <v>336</v>
+        <v>2599</v>
       </c>
       <c r="X1323" t="s">
-        <v>336</v>
+        <v>2599</v>
       </c>
       <c r="Y1323" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1323" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1323" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1323" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1323">
-        <v>108</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1324" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1324" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1324" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1324" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1324" t="s">
         <v>31</v>
       </c>
       <c r="E1324" t="s">
-        <v>2585</v>
+        <v>2600</v>
       </c>
       <c r="F1324">
-        <v>75</v>
+        <v>54</v>
+      </c>
+      <c r="G1324">
+        <v>7</v>
       </c>
       <c r="H1324">
-        <v>75</v>
+        <v>5</v>
+      </c>
+      <c r="I1324">
+        <v>24</v>
+      </c>
+      <c r="L1324">
+        <v>7</v>
+      </c>
+      <c r="M1324">
+        <v>11</v>
       </c>
       <c r="S1324" t="s">
         <v>33</v>
@@ -92044,63 +92053,54 @@
         <v>34</v>
       </c>
       <c r="U1324" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1324" t="s">
-        <v>273</v>
+        <v>1819</v>
       </c>
       <c r="W1324" t="s">
-        <v>332</v>
+        <v>194</v>
       </c>
       <c r="X1324" t="s">
-        <v>332</v>
+        <v>194</v>
       </c>
       <c r="Y1324" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1324" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1324" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1324" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1324">
-        <v>75</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1325" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1325" t="s">
-        <v>2578</v>
+        <v>2587</v>
       </c>
       <c r="B1325" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="C1325" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="D1325" t="s">
         <v>31</v>
       </c>
       <c r="E1325" t="s">
-        <v>2586</v>
+        <v>2601</v>
       </c>
       <c r="F1325">
-        <v>70</v>
-      </c>
-      <c r="G1325">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="H1325">
-        <v>21</v>
-      </c>
-      <c r="I1325">
-        <v>15</v>
-      </c>
-      <c r="L1325">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="S1325" t="s">
         <v>33</v>
@@ -92109,31 +92109,31 @@
         <v>34</v>
       </c>
       <c r="U1325" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1325" t="s">
-        <v>273</v>
+        <v>1853</v>
       </c>
       <c r="W1325" t="s">
-        <v>380</v>
+        <v>2602</v>
       </c>
       <c r="X1325" t="s">
-        <v>380</v>
+        <v>2602</v>
       </c>
       <c r="Y1325" t="s">
-        <v>251</v>
+        <v>1820</v>
       </c>
       <c r="Z1325" t="s">
-        <v>2579</v>
+        <v>2588</v>
       </c>
       <c r="AA1325" t="s">
-        <v>2581</v>
+        <v>2590</v>
       </c>
       <c r="AB1325" t="s">
-        <v>253</v>
+        <v>1822</v>
       </c>
       <c r="AC1325">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1326" spans="1:29" x14ac:dyDescent="0.3">
@@ -92150,22 +92150,22 @@
         <v>31</v>
       </c>
       <c r="E1326" t="s">
-        <v>2589</v>
+        <v>2603</v>
       </c>
       <c r="F1326">
-        <v>157</v>
+        <v>46</v>
       </c>
       <c r="G1326">
-        <v>93</v>
+        <v>21</v>
       </c>
       <c r="H1326">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I1326">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="M1326">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S1326" t="s">
         <v>33</v>
@@ -92177,13 +92177,13 @@
         <v>1766</v>
       </c>
       <c r="V1326" t="s">
-        <v>1819</v>
+        <v>1887</v>
       </c>
       <c r="W1326" t="s">
-        <v>125</v>
+        <v>281</v>
       </c>
       <c r="X1326" t="s">
-        <v>125</v>
+        <v>281</v>
       </c>
       <c r="Y1326" t="s">
         <v>1820</v>
@@ -92198,7 +92198,7 @@
         <v>1822</v>
       </c>
       <c r="AC1326">
-        <v>152</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1327" spans="1:29" x14ac:dyDescent="0.3">
@@ -92215,22 +92215,13 @@
         <v>31</v>
       </c>
       <c r="E1327" t="s">
-        <v>2591</v>
+        <v>2604</v>
       </c>
       <c r="F1327">
-        <v>122</v>
-      </c>
-      <c r="G1327">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H1327">
-        <v>2</v>
-      </c>
-      <c r="I1327">
-        <v>6</v>
-      </c>
-      <c r="M1327">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="S1327" t="s">
         <v>33</v>
@@ -92245,10 +92236,10 @@
         <v>1853</v>
       </c>
       <c r="W1327" t="s">
-        <v>2592</v>
+        <v>2605</v>
       </c>
       <c r="X1327" t="s">
-        <v>2592</v>
+        <v>2605</v>
       </c>
       <c r="Y1327" t="s">
         <v>1820</v>
@@ -92263,36 +92254,30 @@
         <v>1822</v>
       </c>
       <c r="AC1327">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1328" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1328" t="s">
-        <v>2587</v>
+        <v>2606</v>
       </c>
       <c r="B1328" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="C1328" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="D1328" t="s">
         <v>31</v>
       </c>
       <c r="E1328" t="s">
-        <v>2593</v>
+        <v>2608</v>
       </c>
       <c r="F1328">
-        <v>107</v>
-      </c>
-      <c r="G1328">
-        <v>42</v>
-      </c>
-      <c r="I1328">
-        <v>4</v>
-      </c>
-      <c r="M1328">
-        <v>61</v>
+        <v>215</v>
+      </c>
+      <c r="H1328">
+        <v>215</v>
       </c>
       <c r="S1328" t="s">
         <v>33</v>
@@ -92301,54 +92286,54 @@
         <v>34</v>
       </c>
       <c r="U1328" t="s">
-        <v>1766</v>
+        <v>110</v>
       </c>
       <c r="V1328" t="s">
-        <v>1853</v>
+        <v>302</v>
       </c>
       <c r="W1328" t="s">
-        <v>2594</v>
+        <v>287</v>
       </c>
       <c r="X1328" t="s">
-        <v>2594</v>
+        <v>287</v>
       </c>
       <c r="Y1328" t="s">
-        <v>1820</v>
+        <v>303</v>
       </c>
       <c r="Z1328" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="AA1328" t="s">
-        <v>2590</v>
+        <v>2609</v>
       </c>
       <c r="AB1328" t="s">
-        <v>1822</v>
+        <v>305</v>
       </c>
       <c r="AC1328">
-        <v>92</v>
+        <v>215</v>
       </c>
     </row>
     <row r="1329" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1329" t="s">
-        <v>2587</v>
+        <v>2606</v>
       </c>
       <c r="B1329" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="C1329" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="D1329" t="s">
         <v>31</v>
       </c>
       <c r="E1329" t="s">
-        <v>2595</v>
+        <v>2610</v>
       </c>
       <c r="F1329">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H1329">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="S1329" t="s">
         <v>33</v>
@@ -92357,60 +92342,66 @@
         <v>34</v>
       </c>
       <c r="U1329" t="s">
-        <v>1766</v>
+        <v>110</v>
       </c>
       <c r="V1329" t="s">
-        <v>1853</v>
+        <v>302</v>
       </c>
       <c r="W1329" t="s">
-        <v>2596</v>
+        <v>296</v>
       </c>
       <c r="X1329" t="s">
-        <v>2596</v>
+        <v>296</v>
       </c>
       <c r="Y1329" t="s">
-        <v>1820</v>
+        <v>303</v>
       </c>
       <c r="Z1329" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="AA1329" t="s">
-        <v>2590</v>
+        <v>2609</v>
       </c>
       <c r="AB1329" t="s">
-        <v>1822</v>
+        <v>305</v>
       </c>
       <c r="AC1329">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1330" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1330" t="s">
-        <v>2587</v>
+        <v>2606</v>
       </c>
       <c r="B1330" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="C1330" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="D1330" t="s">
         <v>31</v>
       </c>
       <c r="E1330" t="s">
-        <v>2597</v>
+        <v>2611</v>
       </c>
       <c r="F1330">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="G1330">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="H1330">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="I1330">
+        <v>16</v>
+      </c>
+      <c r="L1330">
+        <v>1</v>
       </c>
       <c r="M1330">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S1330" t="s">
         <v>33</v>
@@ -92419,54 +92410,57 @@
         <v>34</v>
       </c>
       <c r="U1330" t="s">
-        <v>1766</v>
+        <v>110</v>
       </c>
       <c r="V1330" t="s">
-        <v>1887</v>
+        <v>302</v>
       </c>
       <c r="W1330" t="s">
-        <v>995</v>
+        <v>1021</v>
       </c>
       <c r="X1330" t="s">
-        <v>995</v>
+        <v>1021</v>
       </c>
       <c r="Y1330" t="s">
-        <v>1820</v>
+        <v>303</v>
       </c>
       <c r="Z1330" t="s">
-        <v>2588</v>
+        <v>2607</v>
       </c>
       <c r="AA1330" t="s">
-        <v>2590</v>
+        <v>2609</v>
       </c>
       <c r="AB1330" t="s">
-        <v>1822</v>
+        <v>305</v>
       </c>
       <c r="AC1330">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1331" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1331" t="s">
-        <v>2587</v>
+        <v>2612</v>
       </c>
       <c r="B1331" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="C1331" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="D1331" t="s">
         <v>31</v>
       </c>
       <c r="E1331" t="s">
-        <v>2598</v>
+        <v>2614</v>
       </c>
       <c r="F1331">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="H1331">
-        <v>57</v>
+        <v>112</v>
+      </c>
+      <c r="I1331">
+        <v>35</v>
       </c>
       <c r="S1331" t="s">
         <v>33</v>
@@ -92475,67 +92469,67 @@
         <v>34</v>
       </c>
       <c r="U1331" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1331" t="s">
-        <v>1853</v>
+        <v>714</v>
       </c>
       <c r="W1331" t="s">
-        <v>2599</v>
+        <v>2615</v>
       </c>
       <c r="X1331" t="s">
-        <v>2599</v>
+        <v>2615</v>
       </c>
       <c r="Y1331" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1331" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="AA1331" t="s">
-        <v>2590</v>
+        <v>2616</v>
       </c>
       <c r="AB1331" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1331">
-        <v>57</v>
+        <v>145</v>
       </c>
     </row>
     <row r="1332" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1332" t="s">
-        <v>2587</v>
+        <v>2612</v>
       </c>
       <c r="B1332" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="C1332" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="D1332" t="s">
         <v>31</v>
       </c>
       <c r="E1332" t="s">
-        <v>2600</v>
+        <v>2617</v>
       </c>
       <c r="F1332">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="G1332">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="H1332">
+        <v>15</v>
+      </c>
+      <c r="I1332">
+        <v>22</v>
+      </c>
+      <c r="L1332">
+        <v>13</v>
+      </c>
+      <c r="M1332">
         <v>5</v>
       </c>
-      <c r="I1332">
-        <v>24</v>
-      </c>
-      <c r="L1332">
-        <v>7</v>
-      </c>
-      <c r="M1332">
-        <v>11</v>
-      </c>
       <c r="S1332" t="s">
         <v>33</v>
       </c>
@@ -92543,54 +92537,54 @@
         <v>34</v>
       </c>
       <c r="U1332" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1332" t="s">
-        <v>1819</v>
+        <v>714</v>
       </c>
       <c r="W1332" t="s">
-        <v>194</v>
+        <v>2618</v>
       </c>
       <c r="X1332" t="s">
-        <v>194</v>
+        <v>2618</v>
       </c>
       <c r="Y1332" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1332" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="AA1332" t="s">
-        <v>2590</v>
+        <v>2616</v>
       </c>
       <c r="AB1332" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1332">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1333" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1333" t="s">
-        <v>2587</v>
+        <v>2612</v>
       </c>
       <c r="B1333" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="C1333" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="D1333" t="s">
         <v>31</v>
       </c>
       <c r="E1333" t="s">
-        <v>2601</v>
+        <v>2619</v>
       </c>
       <c r="F1333">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H1333">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="S1333" t="s">
         <v>33</v>
@@ -92599,63 +92593,63 @@
         <v>34</v>
       </c>
       <c r="U1333" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1333" t="s">
-        <v>1853</v>
+        <v>714</v>
       </c>
       <c r="W1333" t="s">
-        <v>2602</v>
+        <v>2274</v>
       </c>
       <c r="X1333" t="s">
-        <v>2602</v>
+        <v>2274</v>
       </c>
       <c r="Y1333" t="s">
-        <v>1820</v>
+        <v>716</v>
       </c>
       <c r="Z1333" t="s">
-        <v>2588</v>
+        <v>2613</v>
       </c>
       <c r="AA1333" t="s">
-        <v>2590</v>
+        <v>2616</v>
       </c>
       <c r="AB1333" t="s">
-        <v>1822</v>
+        <v>718</v>
       </c>
       <c r="AC1333">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1334" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1334" t="s">
-        <v>2587</v>
+        <v>2620</v>
       </c>
       <c r="B1334" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="C1334" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="D1334" t="s">
         <v>31</v>
       </c>
       <c r="E1334" t="s">
-        <v>2603</v>
+        <v>2622</v>
       </c>
       <c r="F1334">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G1334">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H1334">
-        <v>2</v>
-      </c>
-      <c r="I1334">
-        <v>3</v>
+        <v>62</v>
+      </c>
+      <c r="L1334">
+        <v>16</v>
       </c>
       <c r="M1334">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="S1334" t="s">
         <v>33</v>
@@ -92664,54 +92658,57 @@
         <v>34</v>
       </c>
       <c r="U1334" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1334" t="s">
-        <v>1887</v>
+        <v>1245</v>
       </c>
       <c r="W1334" t="s">
-        <v>281</v>
+        <v>2623</v>
       </c>
       <c r="X1334" t="s">
-        <v>281</v>
+        <v>2623</v>
       </c>
       <c r="Y1334" t="s">
-        <v>1820</v>
+        <v>879</v>
       </c>
       <c r="Z1334" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="AA1334" t="s">
-        <v>2590</v>
+        <v>2624</v>
       </c>
       <c r="AB1334" t="s">
-        <v>1822</v>
+        <v>881</v>
       </c>
       <c r="AC1334">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="1335" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1335" t="s">
-        <v>2587</v>
+        <v>2620</v>
       </c>
       <c r="B1335" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="C1335" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="D1335" t="s">
         <v>31</v>
       </c>
       <c r="E1335" t="s">
-        <v>2604</v>
+        <v>2625</v>
       </c>
       <c r="F1335">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="H1335">
-        <v>5</v>
+        <v>28</v>
+      </c>
+      <c r="L1335">
+        <v>7</v>
       </c>
       <c r="S1335" t="s">
         <v>33</v>
@@ -92720,54 +92717,57 @@
         <v>34</v>
       </c>
       <c r="U1335" t="s">
-        <v>1766</v>
+        <v>713</v>
       </c>
       <c r="V1335" t="s">
-        <v>1853</v>
+        <v>1245</v>
       </c>
       <c r="W1335" t="s">
-        <v>2605</v>
+        <v>134</v>
       </c>
       <c r="X1335" t="s">
-        <v>2605</v>
+        <v>134</v>
       </c>
       <c r="Y1335" t="s">
-        <v>1820</v>
+        <v>879</v>
       </c>
       <c r="Z1335" t="s">
-        <v>2588</v>
+        <v>2621</v>
       </c>
       <c r="AA1335" t="s">
-        <v>2590</v>
+        <v>2624</v>
       </c>
       <c r="AB1335" t="s">
-        <v>1822</v>
+        <v>881</v>
       </c>
       <c r="AC1335">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1336" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1336" t="s">
-        <v>2606</v>
+        <v>2626</v>
       </c>
       <c r="B1336" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="C1336" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="D1336" t="s">
         <v>31</v>
       </c>
       <c r="E1336" t="s">
-        <v>2608</v>
+        <v>2628</v>
       </c>
       <c r="F1336">
-        <v>215</v>
+        <v>185</v>
       </c>
       <c r="H1336">
-        <v>215</v>
+        <v>184</v>
+      </c>
+      <c r="K1336">
+        <v>1</v>
       </c>
       <c r="S1336" t="s">
         <v>33</v>
@@ -92776,54 +92776,63 @@
         <v>34</v>
       </c>
       <c r="U1336" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1336" t="s">
-        <v>302</v>
+        <v>1853</v>
       </c>
       <c r="W1336" t="s">
-        <v>287</v>
+        <v>2629</v>
       </c>
       <c r="X1336" t="s">
-        <v>287</v>
+        <v>2629</v>
       </c>
       <c r="Y1336" t="s">
-        <v>303</v>
+        <v>1820</v>
       </c>
       <c r="Z1336" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="AA1336" t="s">
-        <v>2609</v>
+        <v>2630</v>
       </c>
       <c r="AB1336" t="s">
-        <v>305</v>
+        <v>1822</v>
       </c>
       <c r="AC1336">
-        <v>215</v>
+        <v>184</v>
       </c>
     </row>
     <row r="1337" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1337" t="s">
-        <v>2606</v>
+        <v>2626</v>
       </c>
       <c r="B1337" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="C1337" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="D1337" t="s">
         <v>31</v>
       </c>
       <c r="E1337" t="s">
-        <v>2610</v>
+        <v>2631</v>
       </c>
       <c r="F1337">
-        <v>87</v>
+        <v>113</v>
+      </c>
+      <c r="G1337">
+        <v>46</v>
       </c>
       <c r="H1337">
-        <v>87</v>
+        <v>37</v>
+      </c>
+      <c r="I1337">
+        <v>22</v>
+      </c>
+      <c r="L1337">
+        <v>8</v>
       </c>
       <c r="S1337" t="s">
         <v>33</v>
@@ -92832,66 +92841,60 @@
         <v>34</v>
       </c>
       <c r="U1337" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1337" t="s">
-        <v>302</v>
+        <v>1853</v>
       </c>
       <c r="W1337" t="s">
-        <v>296</v>
+        <v>2632</v>
       </c>
       <c r="X1337" t="s">
-        <v>296</v>
+        <v>2632</v>
       </c>
       <c r="Y1337" t="s">
-        <v>303</v>
+        <v>1820</v>
       </c>
       <c r="Z1337" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="AA1337" t="s">
-        <v>2609</v>
+        <v>2630</v>
       </c>
       <c r="AB1337" t="s">
-        <v>305</v>
+        <v>1822</v>
       </c>
       <c r="AC1337">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1338" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1338" t="s">
-        <v>2606</v>
+        <v>2626</v>
       </c>
       <c r="B1338" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="C1338" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="D1338" t="s">
         <v>31</v>
       </c>
       <c r="E1338" t="s">
-        <v>2611</v>
+        <v>2633</v>
       </c>
       <c r="F1338">
-        <v>79</v>
-      </c>
-      <c r="G1338">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="H1338">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="I1338">
-        <v>16</v>
-      </c>
-      <c r="L1338">
         <v>1</v>
       </c>
-      <c r="M1338">
-        <v>3</v>
+      <c r="K1338">
+        <v>1</v>
       </c>
       <c r="S1338" t="s">
         <v>33</v>
@@ -92900,125 +92903,110 @@
         <v>34</v>
       </c>
       <c r="U1338" t="s">
-        <v>110</v>
+        <v>1766</v>
       </c>
       <c r="V1338" t="s">
-        <v>302</v>
+        <v>1853</v>
       </c>
       <c r="W1338" t="s">
-        <v>1021</v>
+        <v>2634</v>
       </c>
       <c r="X1338" t="s">
-        <v>1021</v>
+        <v>2634</v>
       </c>
       <c r="Y1338" t="s">
-        <v>303</v>
+        <v>1820</v>
       </c>
       <c r="Z1338" t="s">
-        <v>2607</v>
+        <v>2627</v>
       </c>
       <c r="AA1338" t="s">
-        <v>2609</v>
+        <v>2630</v>
       </c>
       <c r="AB1338" t="s">
-        <v>305</v>
+        <v>1822</v>
       </c>
       <c r="AC1338">
-        <v>69</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1339" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1339" t="s">
-        <v>2612</v>
+        <v>2635</v>
       </c>
       <c r="B1339" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="C1339" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="D1339" t="s">
         <v>31</v>
       </c>
       <c r="E1339" t="s">
-        <v>2614</v>
+        <v>2637</v>
       </c>
       <c r="F1339">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="H1339">
-        <v>112</v>
-      </c>
-      <c r="I1339">
+        <v>182</v>
+      </c>
+      <c r="S1339" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1339" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1339" t="s">
         <v>35</v>
       </c>
-      <c r="S1339" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1339" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1339" t="s">
-        <v>713</v>
-      </c>
       <c r="V1339" t="s">
-        <v>714</v>
+        <v>1710</v>
       </c>
       <c r="W1339" t="s">
-        <v>2615</v>
+        <v>2638</v>
       </c>
       <c r="X1339" t="s">
-        <v>2615</v>
+        <v>2638</v>
       </c>
       <c r="Y1339" t="s">
-        <v>716</v>
+        <v>38</v>
       </c>
       <c r="Z1339" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="AA1339" t="s">
-        <v>2616</v>
+        <v>2639</v>
       </c>
       <c r="AB1339" t="s">
-        <v>718</v>
+        <v>40</v>
       </c>
       <c r="AC1339">
-        <v>145</v>
+        <v>182</v>
       </c>
     </row>
     <row r="1340" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1340" t="s">
-        <v>2612</v>
+        <v>2635</v>
       </c>
       <c r="B1340" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="C1340" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="D1340" t="s">
         <v>31</v>
       </c>
       <c r="E1340" t="s">
-        <v>2617</v>
+        <v>2640</v>
       </c>
       <c r="F1340">
-        <v>83</v>
-      </c>
-      <c r="G1340">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="H1340">
-        <v>15</v>
-      </c>
-      <c r="I1340">
-        <v>22</v>
-      </c>
-      <c r="L1340">
-        <v>13</v>
-      </c>
-      <c r="M1340">
-        <v>5</v>
+        <v>104</v>
       </c>
       <c r="S1340" t="s">
         <v>33</v>
@@ -93027,54 +93015,54 @@
         <v>34</v>
       </c>
       <c r="U1340" t="s">
-        <v>713</v>
+        <v>35</v>
       </c>
       <c r="V1340" t="s">
-        <v>714</v>
+        <v>1710</v>
       </c>
       <c r="W1340" t="s">
-        <v>2618</v>
+        <v>2641</v>
       </c>
       <c r="X1340" t="s">
-        <v>2618</v>
+        <v>2641</v>
       </c>
       <c r="Y1340" t="s">
-        <v>716</v>
+        <v>38</v>
       </c>
       <c r="Z1340" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="AA1340" t="s">
-        <v>2616</v>
+        <v>2639</v>
       </c>
       <c r="AB1340" t="s">
-        <v>718</v>
+        <v>40</v>
       </c>
       <c r="AC1340">
-        <v>50</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1341" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1341" t="s">
-        <v>2612</v>
+        <v>2635</v>
       </c>
       <c r="B1341" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="C1341" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="D1341" t="s">
         <v>31</v>
       </c>
       <c r="E1341" t="s">
-        <v>2619</v>
+        <v>2642</v>
       </c>
       <c r="F1341">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="H1341">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="S1341" t="s">
         <v>33</v>
@@ -93083,62 +93071,62 @@
         <v>34</v>
       </c>
       <c r="U1341" t="s">
-        <v>713</v>
+        <v>35</v>
       </c>
       <c r="V1341" t="s">
-        <v>714</v>
+        <v>1710</v>
       </c>
       <c r="W1341" t="s">
-        <v>2274</v>
+        <v>2643</v>
       </c>
       <c r="X1341" t="s">
-        <v>2274</v>
+        <v>2643</v>
       </c>
       <c r="Y1341" t="s">
-        <v>716</v>
+        <v>38</v>
       </c>
       <c r="Z1341" t="s">
-        <v>2613</v>
+        <v>2636</v>
       </c>
       <c r="AA1341" t="s">
-        <v>2616</v>
+        <v>2639</v>
       </c>
       <c r="AB1341" t="s">
-        <v>718</v>
+        <v>40</v>
       </c>
       <c r="AC1341">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1342" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1342" t="s">
-        <v>2620</v>
+        <v>2635</v>
       </c>
       <c r="B1342" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="C1342" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="D1342" t="s">
         <v>31</v>
       </c>
       <c r="E1342" t="s">
-        <v>2622</v>
+        <v>2644</v>
       </c>
       <c r="F1342">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G1342">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H1342">
-        <v>62</v>
+        <v>30</v>
+      </c>
+      <c r="I1342">
+        <v>6</v>
       </c>
       <c r="L1342">
-        <v>16</v>
-      </c>
-      <c r="M1342">
         <v>1</v>
       </c>
       <c r="S1342" t="s">
@@ -93148,116 +93136,125 @@
         <v>34</v>
       </c>
       <c r="U1342" t="s">
-        <v>713</v>
+        <v>35</v>
       </c>
       <c r="V1342" t="s">
-        <v>1245</v>
+        <v>1710</v>
       </c>
       <c r="W1342" t="s">
-        <v>2623</v>
+        <v>2645</v>
       </c>
       <c r="X1342" t="s">
-        <v>2623</v>
+        <v>2645</v>
       </c>
       <c r="Y1342" t="s">
-        <v>879</v>
+        <v>38</v>
       </c>
       <c r="Z1342" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="AA1342" t="s">
-        <v>2624</v>
+        <v>2639</v>
       </c>
       <c r="AB1342" t="s">
-        <v>881</v>
+        <v>40</v>
       </c>
       <c r="AC1342">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1343" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1343" t="s">
-        <v>2620</v>
+        <v>2635</v>
       </c>
       <c r="B1343" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="C1343" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="D1343" t="s">
         <v>31</v>
       </c>
       <c r="E1343" t="s">
-        <v>2625</v>
+        <v>2646</v>
       </c>
       <c r="F1343">
+        <v>44</v>
+      </c>
+      <c r="G1343">
+        <v>18</v>
+      </c>
+      <c r="H1343">
+        <v>25</v>
+      </c>
+      <c r="I1343">
+        <v>1</v>
+      </c>
+      <c r="S1343" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1343" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1343" t="s">
         <v>35</v>
       </c>
-      <c r="H1343">
-        <v>28</v>
-      </c>
-      <c r="L1343">
-        <v>7</v>
-      </c>
-      <c r="S1343" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1343" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1343" t="s">
-        <v>713</v>
-      </c>
       <c r="V1343" t="s">
-        <v>1245</v>
+        <v>1710</v>
       </c>
       <c r="W1343" t="s">
-        <v>134</v>
+        <v>2647</v>
       </c>
       <c r="X1343" t="s">
-        <v>134</v>
+        <v>2647</v>
       </c>
       <c r="Y1343" t="s">
-        <v>879</v>
+        <v>38</v>
       </c>
       <c r="Z1343" t="s">
-        <v>2621</v>
+        <v>2636</v>
       </c>
       <c r="AA1343" t="s">
-        <v>2624</v>
+        <v>2639</v>
       </c>
       <c r="AB1343" t="s">
-        <v>881</v>
+        <v>40</v>
       </c>
       <c r="AC1343">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1344" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1344" t="s">
-        <v>2626</v>
+        <v>2648</v>
       </c>
       <c r="B1344" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="C1344" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="D1344" t="s">
         <v>31</v>
       </c>
       <c r="E1344" t="s">
-        <v>2628</v>
+        <v>2650</v>
       </c>
       <c r="F1344">
-        <v>185</v>
+        <v>142</v>
+      </c>
+      <c r="G1344">
+        <v>134</v>
       </c>
       <c r="H1344">
-        <v>184</v>
-      </c>
-      <c r="K1344">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="I1344">
+        <v>3</v>
+      </c>
+      <c r="M1344">
+        <v>2</v>
       </c>
       <c r="S1344" t="s">
         <v>33</v>
@@ -93269,60 +93266,51 @@
         <v>1766</v>
       </c>
       <c r="V1344" t="s">
-        <v>1853</v>
+        <v>1887</v>
       </c>
       <c r="W1344" t="s">
-        <v>2629</v>
+        <v>1088</v>
       </c>
       <c r="X1344" t="s">
-        <v>2629</v>
+        <v>1088</v>
       </c>
       <c r="Y1344" t="s">
-        <v>1820</v>
+        <v>1888</v>
       </c>
       <c r="Z1344" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="AA1344" t="s">
-        <v>2630</v>
+        <v>2651</v>
       </c>
       <c r="AB1344" t="s">
-        <v>1822</v>
+        <v>1890</v>
       </c>
       <c r="AC1344">
-        <v>184</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1345" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1345" t="s">
-        <v>2626</v>
+        <v>2648</v>
       </c>
       <c r="B1345" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="C1345" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="D1345" t="s">
         <v>31</v>
       </c>
       <c r="E1345" t="s">
-        <v>2631</v>
+        <v>2652</v>
       </c>
       <c r="F1345">
-        <v>113</v>
-      </c>
-      <c r="G1345">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="H1345">
-        <v>37</v>
-      </c>
-      <c r="I1345">
-        <v>22</v>
-      </c>
-      <c r="L1345">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="S1345" t="s">
         <v>33</v>
@@ -93334,57 +93322,51 @@
         <v>1766</v>
       </c>
       <c r="V1345" t="s">
-        <v>1853</v>
+        <v>1887</v>
       </c>
       <c r="W1345" t="s">
-        <v>2632</v>
+        <v>1091</v>
       </c>
       <c r="X1345" t="s">
-        <v>2632</v>
+        <v>1091</v>
       </c>
       <c r="Y1345" t="s">
-        <v>1820</v>
+        <v>1888</v>
       </c>
       <c r="Z1345" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="AA1345" t="s">
-        <v>2630</v>
+        <v>2651</v>
       </c>
       <c r="AB1345" t="s">
-        <v>1822</v>
+        <v>1890</v>
       </c>
       <c r="AC1345">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1346" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1346" t="s">
-        <v>2626</v>
+        <v>2648</v>
       </c>
       <c r="B1346" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="C1346" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="D1346" t="s">
         <v>31</v>
       </c>
       <c r="E1346" t="s">
-        <v>2633</v>
+        <v>2653</v>
       </c>
       <c r="F1346">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H1346">
-        <v>98</v>
-      </c>
-      <c r="I1346">
-        <v>1</v>
-      </c>
-      <c r="K1346">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="S1346" t="s">
         <v>33</v>
@@ -93396,51 +93378,57 @@
         <v>1766</v>
       </c>
       <c r="V1346" t="s">
-        <v>1853</v>
+        <v>1887</v>
       </c>
       <c r="W1346" t="s">
-        <v>2634</v>
+        <v>1989</v>
       </c>
       <c r="X1346" t="s">
-        <v>2634</v>
+        <v>1989</v>
       </c>
       <c r="Y1346" t="s">
-        <v>1820</v>
+        <v>1888</v>
       </c>
       <c r="Z1346" t="s">
-        <v>2627</v>
+        <v>2649</v>
       </c>
       <c r="AA1346" t="s">
-        <v>2630</v>
+        <v>2651</v>
       </c>
       <c r="AB1346" t="s">
-        <v>1822</v>
+        <v>1890</v>
       </c>
       <c r="AC1346">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="1347" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1347" t="s">
-        <v>2635</v>
+        <v>2648</v>
       </c>
       <c r="B1347" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="C1347" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="D1347" t="s">
         <v>31</v>
       </c>
       <c r="E1347" t="s">
-        <v>2637</v>
+        <v>2654</v>
       </c>
       <c r="F1347">
-        <v>182</v>
+        <v>89</v>
       </c>
       <c r="H1347">
-        <v>182</v>
+        <v>35</v>
+      </c>
+      <c r="I1347">
+        <v>44</v>
+      </c>
+      <c r="L1347">
+        <v>10</v>
       </c>
       <c r="S1347" t="s">
         <v>33</v>
@@ -93449,54 +93437,54 @@
         <v>34</v>
       </c>
       <c r="U1347" t="s">
-        <v>35</v>
+        <v>1766</v>
       </c>
       <c r="V1347" t="s">
-        <v>1710</v>
+        <v>1887</v>
       </c>
       <c r="W1347" t="s">
-        <v>2638</v>
+        <v>2655</v>
       </c>
       <c r="X1347" t="s">
-        <v>2638</v>
+        <v>2655</v>
       </c>
       <c r="Y1347" t="s">
-        <v>38</v>
+        <v>1888</v>
       </c>
       <c r="Z1347" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="AA1347" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="AB1347" t="s">
-        <v>40</v>
+        <v>1890</v>
       </c>
       <c r="AC1347">
-        <v>182</v>
+        <v>64</v>
       </c>
     </row>
     <row r="1348" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1348" t="s">
-        <v>2635</v>
+        <v>2648</v>
       </c>
       <c r="B1348" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="C1348" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="D1348" t="s">
         <v>31</v>
       </c>
       <c r="E1348" t="s">
-        <v>2640</v>
+        <v>2656</v>
       </c>
       <c r="F1348">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="H1348">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="S1348" t="s">
         <v>33</v>
@@ -93505,54 +93493,66 @@
         <v>34</v>
       </c>
       <c r="U1348" t="s">
-        <v>35</v>
+        <v>1766</v>
       </c>
       <c r="V1348" t="s">
-        <v>1710</v>
+        <v>1887</v>
       </c>
       <c r="W1348" t="s">
-        <v>2641</v>
+        <v>2657</v>
       </c>
       <c r="X1348" t="s">
-        <v>2641</v>
+        <v>2657</v>
       </c>
       <c r="Y1348" t="s">
-        <v>38</v>
+        <v>1888</v>
       </c>
       <c r="Z1348" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="AA1348" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="AB1348" t="s">
-        <v>40</v>
+        <v>1890</v>
       </c>
       <c r="AC1348">
-        <v>104</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1349" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1349" t="s">
-        <v>2635</v>
+        <v>2648</v>
       </c>
       <c r="B1349" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="C1349" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="D1349" t="s">
         <v>31</v>
       </c>
       <c r="E1349" t="s">
-        <v>2642</v>
+        <v>2658</v>
       </c>
       <c r="F1349">
-        <v>79</v>
-      </c>
-      <c r="H1349">
-        <v>79</v>
+        <v>71</v>
+      </c>
+      <c r="G1349">
+        <v>47</v>
+      </c>
+      <c r="I1349">
+        <v>10</v>
+      </c>
+      <c r="K1349">
+        <v>1</v>
+      </c>
+      <c r="L1349">
+        <v>3</v>
+      </c>
+      <c r="M1349">
+        <v>10</v>
       </c>
       <c r="S1349" t="s">
         <v>33</v>
@@ -93561,63 +93561,60 @@
         <v>34</v>
       </c>
       <c r="U1349" t="s">
-        <v>35</v>
+        <v>1766</v>
       </c>
       <c r="V1349" t="s">
-        <v>1710</v>
+        <v>1887</v>
       </c>
       <c r="W1349" t="s">
-        <v>2643</v>
+        <v>1991</v>
       </c>
       <c r="X1349" t="s">
-        <v>2643</v>
+        <v>1991</v>
       </c>
       <c r="Y1349" t="s">
-        <v>38</v>
+        <v>1888</v>
       </c>
       <c r="Z1349" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="AA1349" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="AB1349" t="s">
-        <v>40</v>
+        <v>1890</v>
       </c>
       <c r="AC1349">
-        <v>79</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1350" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1350" t="s">
-        <v>2635</v>
+        <v>2648</v>
       </c>
       <c r="B1350" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="C1350" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="D1350" t="s">
         <v>31</v>
       </c>
       <c r="E1350" t="s">
-        <v>2644</v>
+        <v>2659</v>
       </c>
       <c r="F1350">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="G1350">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H1350">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I1350">
-        <v>6</v>
-      </c>
-      <c r="L1350">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="S1350" t="s">
         <v>33</v>
@@ -93626,60 +93623,63 @@
         <v>34</v>
       </c>
       <c r="U1350" t="s">
-        <v>35</v>
+        <v>1766</v>
       </c>
       <c r="V1350" t="s">
-        <v>1710</v>
+        <v>1887</v>
       </c>
       <c r="W1350" t="s">
-        <v>2645</v>
+        <v>2660</v>
       </c>
       <c r="X1350" t="s">
-        <v>2645</v>
+        <v>2660</v>
       </c>
       <c r="Y1350" t="s">
-        <v>38</v>
+        <v>1888</v>
       </c>
       <c r="Z1350" t="s">
-        <v>2636</v>
+        <v>2649</v>
       </c>
       <c r="AA1350" t="s">
-        <v>2639</v>
+        <v>2651</v>
       </c>
       <c r="AB1350" t="s">
-        <v>40</v>
+        <v>1890</v>
       </c>
       <c r="AC1350">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1351" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1351" t="s">
-        <v>2635</v>
+        <v>2661</v>
       </c>
       <c r="B1351" t="s">
-        <v>2636</v>
+        <v>2662</v>
       </c>
       <c r="C1351" t="s">
-        <v>2636</v>
+        <v>2662</v>
       </c>
       <c r="D1351" t="s">
         <v>31</v>
       </c>
       <c r="E1351" t="s">
-        <v>2646</v>
+        <v>2663</v>
       </c>
       <c r="F1351">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="G1351">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H1351">
-        <v>25</v>
-      </c>
-      <c r="I1351">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="L1351">
+        <v>49</v>
+      </c>
+      <c r="M1351">
+        <v>23</v>
       </c>
       <c r="S1351" t="s">
         <v>33</v>
@@ -93688,66 +93688,72 @@
         <v>34</v>
       </c>
       <c r="U1351" t="s">
-        <v>35</v>
+        <v>1766</v>
       </c>
       <c r="V1351" t="s">
-        <v>1710</v>
+        <v>2169</v>
       </c>
       <c r="W1351" t="s">
-        <v>2647</v>
+        <v>1854</v>
       </c>
       <c r="X1351" t="s">
-        <v>2647</v>
+        <v>1854</v>
       </c>
       <c r="Y1351" t="s">
-        <v>38</v>
+        <v>1927</v>
       </c>
       <c r="Z1351" t="s">
-        <v>2636</v>
+        <v>2662</v>
       </c>
       <c r="AA1351" t="s">
-        <v>2639</v>
+        <v>2664</v>
       </c>
       <c r="AB1351" t="s">
-        <v>40</v>
+        <v>1929</v>
       </c>
       <c r="AC1351">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1352" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1352" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1352" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1352" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1352" t="s">
         <v>31</v>
       </c>
       <c r="E1352" t="s">
-        <v>2650</v>
+        <v>2665</v>
       </c>
       <c r="F1352">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="G1352">
-        <v>134</v>
+        <v>41</v>
       </c>
       <c r="H1352">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I1352">
-        <v>3</v>
+        <v>20</v>
+      </c>
+      <c r="J1352">
+        <v>1</v>
+      </c>
+      <c r="L1352">
+        <v>13</v>
       </c>
       <c r="M1352">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S1352" t="s">
-        <v>33</v>
+        <v>2674</v>
       </c>
       <c r="T1352" t="s">
         <v>34</v>
@@ -93756,54 +93762,66 @@
         <v>1766</v>
       </c>
       <c r="V1352" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1352" t="s">
-        <v>1088</v>
+        <v>294</v>
       </c>
       <c r="X1352" t="s">
-        <v>1088</v>
+        <v>294</v>
       </c>
       <c r="Y1352" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1352" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1352" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1352" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1352">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1353" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1353" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1353" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1353" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1353" t="s">
         <v>31</v>
       </c>
       <c r="E1353" t="s">
-        <v>2652</v>
+        <v>2666</v>
       </c>
       <c r="F1353">
-        <v>122</v>
+        <v>93</v>
+      </c>
+      <c r="G1353">
+        <v>30</v>
       </c>
       <c r="H1353">
-        <v>122</v>
+        <v>43</v>
+      </c>
+      <c r="I1353">
+        <v>5</v>
+      </c>
+      <c r="L1353">
+        <v>14</v>
+      </c>
+      <c r="M1353">
+        <v>1</v>
       </c>
       <c r="S1353" t="s">
-        <v>33</v>
+        <v>2674</v>
       </c>
       <c r="T1353" t="s">
         <v>34</v>
@@ -93812,54 +93830,63 @@
         <v>1766</v>
       </c>
       <c r="V1353" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1353" t="s">
-        <v>1091</v>
+        <v>290</v>
       </c>
       <c r="X1353" t="s">
-        <v>1091</v>
+        <v>290</v>
       </c>
       <c r="Y1353" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1353" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1353" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1353" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1353">
-        <v>122</v>
+        <v>84</v>
       </c>
     </row>
     <row r="1354" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1354" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1354" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1354" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1354" t="s">
         <v>31</v>
       </c>
       <c r="E1354" t="s">
-        <v>2653</v>
+        <v>2667</v>
       </c>
       <c r="F1354">
-        <v>96</v>
+        <v>93</v>
+      </c>
+      <c r="G1354">
+        <v>37</v>
       </c>
       <c r="H1354">
-        <v>96</v>
+        <v>27</v>
+      </c>
+      <c r="I1354">
+        <v>17</v>
+      </c>
+      <c r="M1354">
+        <v>12</v>
       </c>
       <c r="S1354" t="s">
-        <v>33</v>
+        <v>2674</v>
       </c>
       <c r="T1354" t="s">
         <v>34</v>
@@ -93868,60 +93895,66 @@
         <v>1766</v>
       </c>
       <c r="V1354" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1354" t="s">
-        <v>1989</v>
+        <v>292</v>
       </c>
       <c r="X1354" t="s">
-        <v>1989</v>
+        <v>292</v>
       </c>
       <c r="Y1354" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1354" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1354" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1354" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1354">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="1355" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1355" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1355" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1355" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1355" t="s">
         <v>31</v>
       </c>
       <c r="E1355" t="s">
-        <v>2654</v>
+        <v>2668</v>
       </c>
       <c r="F1355">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="G1355">
+        <v>16</v>
       </c>
       <c r="H1355">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I1355">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="L1355">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="M1355">
+        <v>26</v>
       </c>
       <c r="S1355" t="s">
-        <v>33</v>
+        <v>2674</v>
       </c>
       <c r="T1355" t="s">
         <v>34</v>
@@ -93930,54 +93963,60 @@
         <v>1766</v>
       </c>
       <c r="V1355" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1355" t="s">
-        <v>2655</v>
+        <v>196</v>
       </c>
       <c r="X1355" t="s">
-        <v>2655</v>
+        <v>196</v>
       </c>
       <c r="Y1355" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1355" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1355" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1355" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1355">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="1356" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1356" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1356" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1356" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1356" t="s">
         <v>31</v>
       </c>
       <c r="E1356" t="s">
-        <v>2656</v>
+        <v>2669</v>
       </c>
       <c r="F1356">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H1356">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="I1356">
+        <v>5</v>
+      </c>
+      <c r="L1356">
+        <v>6</v>
       </c>
       <c r="S1356" t="s">
-        <v>33</v>
+        <v>2674</v>
       </c>
       <c r="T1356" t="s">
         <v>34</v>
@@ -93986,63 +94025,54 @@
         <v>1766</v>
       </c>
       <c r="V1356" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1356" t="s">
-        <v>2657</v>
+        <v>274</v>
       </c>
       <c r="X1356" t="s">
-        <v>2657</v>
+        <v>274</v>
       </c>
       <c r="Y1356" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1356" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1356" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1356" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1356">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1357" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1357" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1357" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1357" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1357" t="s">
         <v>31</v>
       </c>
       <c r="E1357" t="s">
-        <v>2658</v>
+        <v>2670</v>
       </c>
       <c r="F1357">
-        <v>71</v>
-      </c>
-      <c r="G1357">
-        <v>47</v>
-      </c>
-      <c r="I1357">
-        <v>10</v>
-      </c>
-      <c r="K1357">
+        <v>14</v>
+      </c>
+      <c r="H1357">
         <v>1</v>
       </c>
       <c r="L1357">
-        <v>3</v>
-      </c>
-      <c r="M1357">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S1357" t="s">
         <v>33</v>
@@ -94054,57 +94084,51 @@
         <v>1766</v>
       </c>
       <c r="V1357" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1357" t="s">
-        <v>1991</v>
+        <v>2671</v>
       </c>
       <c r="X1357" t="s">
-        <v>1991</v>
+        <v>2671</v>
       </c>
       <c r="Y1357" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1357" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1357" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1357" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1357">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1358" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1358" t="s">
-        <v>2648</v>
+        <v>2661</v>
       </c>
       <c r="B1358" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="C1358" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="D1358" t="s">
         <v>31</v>
       </c>
       <c r="E1358" t="s">
-        <v>2659</v>
+        <v>2672</v>
       </c>
       <c r="F1358">
-        <v>65</v>
-      </c>
-      <c r="G1358">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1358">
-        <v>42</v>
-      </c>
-      <c r="I1358">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="S1358" t="s">
         <v>33</v>
@@ -94116,541 +94140,27 @@
         <v>1766</v>
       </c>
       <c r="V1358" t="s">
-        <v>1887</v>
+        <v>2169</v>
       </c>
       <c r="W1358" t="s">
-        <v>2660</v>
+        <v>2673</v>
       </c>
       <c r="X1358" t="s">
-        <v>2660</v>
+        <v>2673</v>
       </c>
       <c r="Y1358" t="s">
-        <v>1888</v>
+        <v>1927</v>
       </c>
       <c r="Z1358" t="s">
-        <v>2649</v>
+        <v>2662</v>
       </c>
       <c r="AA1358" t="s">
-        <v>2651</v>
+        <v>2664</v>
       </c>
       <c r="AB1358" t="s">
-        <v>1890</v>
+        <v>1929</v>
       </c>
       <c r="AC1358">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="1359" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1359" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1359" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1359" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1359" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1359" t="s">
-        <v>2663</v>
-      </c>
-      <c r="F1359">
-        <v>111</v>
-      </c>
-      <c r="G1359">
-        <v>27</v>
-      </c>
-      <c r="H1359">
-        <v>12</v>
-      </c>
-      <c r="L1359">
-        <v>49</v>
-      </c>
-      <c r="M1359">
-        <v>23</v>
-      </c>
-      <c r="S1359" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1359" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1359" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1359" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1359" t="s">
-        <v>1854</v>
-      </c>
-      <c r="X1359" t="s">
-        <v>1854</v>
-      </c>
-      <c r="Y1359" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1359" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1359" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1359" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1359">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="1360" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1360" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1360" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1360" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1360" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1360" t="s">
-        <v>2665</v>
-      </c>
-      <c r="F1360">
-        <v>96</v>
-      </c>
-      <c r="G1360">
-        <v>41</v>
-      </c>
-      <c r="H1360">
-        <v>20</v>
-      </c>
-      <c r="I1360">
-        <v>20</v>
-      </c>
-      <c r="J1360">
-        <v>1</v>
-      </c>
-      <c r="L1360">
-        <v>13</v>
-      </c>
-      <c r="M1360">
-        <v>1</v>
-      </c>
-      <c r="S1360" t="s">
-        <v>2674</v>
-      </c>
-      <c r="T1360" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1360" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1360" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1360" t="s">
-        <v>294</v>
-      </c>
-      <c r="X1360" t="s">
-        <v>294</v>
-      </c>
-      <c r="Y1360" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1360" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1360" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1360" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1360">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="1361" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1361" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1361" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1361" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1361" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1361" t="s">
-        <v>2666</v>
-      </c>
-      <c r="F1361">
-        <v>93</v>
-      </c>
-      <c r="G1361">
-        <v>30</v>
-      </c>
-      <c r="H1361">
-        <v>43</v>
-      </c>
-      <c r="I1361">
-        <v>5</v>
-      </c>
-      <c r="L1361">
-        <v>14</v>
-      </c>
-      <c r="M1361">
-        <v>1</v>
-      </c>
-      <c r="S1361" t="s">
-        <v>2674</v>
-      </c>
-      <c r="T1361" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1361" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1361" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1361" t="s">
-        <v>290</v>
-      </c>
-      <c r="X1361" t="s">
-        <v>290</v>
-      </c>
-      <c r="Y1361" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1361" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1361" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1361" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1361">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="1362" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1362" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1362" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1362" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1362" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1362" t="s">
-        <v>2667</v>
-      </c>
-      <c r="F1362">
-        <v>93</v>
-      </c>
-      <c r="G1362">
-        <v>37</v>
-      </c>
-      <c r="H1362">
-        <v>27</v>
-      </c>
-      <c r="I1362">
-        <v>17</v>
-      </c>
-      <c r="M1362">
-        <v>12</v>
-      </c>
-      <c r="S1362" t="s">
-        <v>2674</v>
-      </c>
-      <c r="T1362" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1362" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1362" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1362" t="s">
-        <v>292</v>
-      </c>
-      <c r="X1362" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y1362" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1362" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1362" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1362" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1362">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="1363" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1363" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1363" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1363" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1363" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1363" t="s">
-        <v>2668</v>
-      </c>
-      <c r="F1363">
-        <v>91</v>
-      </c>
-      <c r="G1363">
-        <v>16</v>
-      </c>
-      <c r="H1363">
-        <v>34</v>
-      </c>
-      <c r="I1363">
-        <v>10</v>
-      </c>
-      <c r="L1363">
-        <v>5</v>
-      </c>
-      <c r="M1363">
-        <v>26</v>
-      </c>
-      <c r="S1363" t="s">
-        <v>2674</v>
-      </c>
-      <c r="T1363" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1363" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1363" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1363" t="s">
-        <v>196</v>
-      </c>
-      <c r="X1363" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y1363" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1363" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1363" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1363" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1363">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="1364" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1364" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1364" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1364" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1364" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1364" t="s">
-        <v>2669</v>
-      </c>
-      <c r="F1364">
-        <v>80</v>
-      </c>
-      <c r="H1364">
-        <v>69</v>
-      </c>
-      <c r="I1364">
-        <v>5</v>
-      </c>
-      <c r="L1364">
-        <v>6</v>
-      </c>
-      <c r="S1364" t="s">
-        <v>2674</v>
-      </c>
-      <c r="T1364" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1364" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1364" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1364" t="s">
-        <v>274</v>
-      </c>
-      <c r="X1364" t="s">
-        <v>274</v>
-      </c>
-      <c r="Y1364" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1364" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1364" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1364" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1364">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="1365" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1365" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1365" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1365" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1365" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1365" t="s">
-        <v>2670</v>
-      </c>
-      <c r="F1365">
-        <v>14</v>
-      </c>
-      <c r="H1365">
-        <v>1</v>
-      </c>
-      <c r="L1365">
-        <v>13</v>
-      </c>
-      <c r="S1365" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1365" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1365" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1365" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1365" t="s">
-        <v>2671</v>
-      </c>
-      <c r="X1365" t="s">
-        <v>2671</v>
-      </c>
-      <c r="Y1365" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1365" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1365" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1365" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1365">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1366" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1366" t="s">
-        <v>2661</v>
-      </c>
-      <c r="B1366" t="s">
-        <v>2662</v>
-      </c>
-      <c r="C1366" t="s">
-        <v>2662</v>
-      </c>
-      <c r="D1366" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1366" t="s">
-        <v>2672</v>
-      </c>
-      <c r="F1366">
-        <v>1</v>
-      </c>
-      <c r="H1366">
-        <v>1</v>
-      </c>
-      <c r="S1366" t="s">
-        <v>33</v>
-      </c>
-      <c r="T1366" t="s">
-        <v>34</v>
-      </c>
-      <c r="U1366" t="s">
-        <v>1766</v>
-      </c>
-      <c r="V1366" t="s">
-        <v>2169</v>
-      </c>
-      <c r="W1366" t="s">
-        <v>2673</v>
-      </c>
-      <c r="X1366" t="s">
-        <v>2673</v>
-      </c>
-      <c r="Y1366" t="s">
-        <v>1927</v>
-      </c>
-      <c r="Z1366" t="s">
-        <v>2662</v>
-      </c>
-      <c r="AA1366" t="s">
-        <v>2664</v>
-      </c>
-      <c r="AB1366" t="s">
-        <v>1929</v>
-      </c>
-      <c r="AC1366">
         <v>0</v>
       </c>
     </row>
